--- a/development/one_file_rosetta_output/CPCT02010648T_rosetta.xlsx
+++ b/development/one_file_rosetta_output/CPCT02010648T_rosetta.xlsx
@@ -398,14 +398,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E570"/>
+  <dimension ref="A1:F570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
     <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
     <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -426,10 +427,15 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>N indels</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>Example n</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Indel in context</t>
         </is>
@@ -452,9 +458,12 @@
         </is>
       </c>
       <c r="D2" s="4">
+        <v>3</v>
+      </c>
+      <c r="E2" s="4">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -510,7 +519,10 @@
       <c r="D3" s="4">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="4">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -536,9 +548,12 @@
         </is>
       </c>
       <c r="D4" s="4">
+        <v>7</v>
+      </c>
+      <c r="E4" s="4">
         <v>1</v>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -592,9 +607,12 @@
         </is>
       </c>
       <c r="D5" s="4">
+        <v>7</v>
+      </c>
+      <c r="E5" s="4">
         <v>2</v>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -648,9 +666,12 @@
         </is>
       </c>
       <c r="D6" s="4">
+        <v>7</v>
+      </c>
+      <c r="E6" s="4">
         <v>3</v>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -704,9 +725,12 @@
         </is>
       </c>
       <c r="D7" s="4">
+        <v>7</v>
+      </c>
+      <c r="E7" s="4">
         <v>4</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -762,7 +786,10 @@
       <c r="D8" s="4">
         <v>1</v>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="4">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -825,7 +852,10 @@
       <c r="D9" s="4">
         <v>1</v>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="4">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -853,7 +883,10 @@
       <c r="D10" s="4">
         <v>1</v>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="4">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -881,7 +914,10 @@
       <c r="D11" s="4">
         <v>1</v>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="4">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -950,9 +986,12 @@
         </is>
       </c>
       <c r="D12" s="4">
+        <v>2</v>
+      </c>
+      <c r="E12" s="4">
         <v>1</v>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1030,7 +1069,10 @@
       <c r="D13" s="4">
         <v>2</v>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="4">
+        <v>2</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1108,7 +1150,10 @@
       <c r="D14" s="4">
         <v>1</v>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="4">
+        <v>1</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1134,9 +1179,12 @@
         </is>
       </c>
       <c r="D15" s="4">
+        <v>2</v>
+      </c>
+      <c r="E15" s="4">
         <v>1</v>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1235,9 +1283,12 @@
         </is>
       </c>
       <c r="D16" s="4">
+        <v>3</v>
+      </c>
+      <c r="E16" s="4">
         <v>1</v>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1351,9 +1402,12 @@
         </is>
       </c>
       <c r="D17" s="4">
+        <v>3</v>
+      </c>
+      <c r="E17" s="4">
         <v>1</v>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1381,7 +1435,10 @@
       <c r="D18" s="4">
         <v>1</v>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="4">
+        <v>1</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1435,9 +1492,12 @@
         </is>
       </c>
       <c r="D19" s="4">
+        <v>4</v>
+      </c>
+      <c r="E19" s="4">
         <v>1</v>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1491,9 +1551,12 @@
         </is>
       </c>
       <c r="D20" s="4">
+        <v>4</v>
+      </c>
+      <c r="E20" s="4">
         <v>2</v>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1547,9 +1610,12 @@
         </is>
       </c>
       <c r="D21" s="4">
+        <v>4</v>
+      </c>
+      <c r="E21" s="4">
         <v>3</v>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1605,7 +1671,10 @@
       <c r="D22" s="4">
         <v>1</v>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="4">
+        <v>1</v>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1633,7 +1702,10 @@
       <c r="D23" s="4">
         <v>1</v>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="4">
+        <v>1</v>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1694,9 +1766,12 @@
         </is>
       </c>
       <c r="D24" s="4">
+        <v>4</v>
+      </c>
+      <c r="E24" s="4">
         <v>1</v>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1757,9 +1832,12 @@
         </is>
       </c>
       <c r="D25" s="4">
+        <v>4</v>
+      </c>
+      <c r="E25" s="4">
         <v>2</v>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1820,9 +1898,12 @@
         </is>
       </c>
       <c r="D26" s="4">
+        <v>4</v>
+      </c>
+      <c r="E26" s="4">
         <v>3</v>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1885,7 +1966,10 @@
       <c r="D27" s="4">
         <v>4</v>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="4">
+        <v>4</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1948,7 +2032,10 @@
       <c r="D28" s="4">
         <v>1</v>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="4">
+        <v>1</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2019,7 +2106,10 @@
       <c r="D29" s="4">
         <v>1</v>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E29" s="4">
+        <v>1</v>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2095,9 +2185,12 @@
         </is>
       </c>
       <c r="D30" s="4">
+        <v>2</v>
+      </c>
+      <c r="E30" s="4">
         <v>1</v>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2173,9 +2266,12 @@
         </is>
       </c>
       <c r="D31" s="4">
+        <v>2</v>
+      </c>
+      <c r="E31" s="4">
         <v>1</v>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2261,7 +2357,10 @@
       <c r="D32" s="4">
         <v>2</v>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E32" s="4">
+        <v>2</v>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2347,7 +2446,10 @@
       <c r="D33" s="4">
         <v>1</v>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E33" s="4">
+        <v>1</v>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2438,9 +2540,12 @@
         </is>
       </c>
       <c r="D34" s="4">
+        <v>3</v>
+      </c>
+      <c r="E34" s="4">
         <v>1</v>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2494,9 +2599,12 @@
         </is>
       </c>
       <c r="D35" s="4">
+        <v>3</v>
+      </c>
+      <c r="E35" s="4">
         <v>2</v>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2550,9 +2658,12 @@
         </is>
       </c>
       <c r="D36" s="4">
+        <v>12</v>
+      </c>
+      <c r="E36" s="4">
         <v>1</v>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2606,9 +2717,12 @@
         </is>
       </c>
       <c r="D37" s="4">
+        <v>12</v>
+      </c>
+      <c r="E37" s="4">
         <v>2</v>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2662,9 +2776,12 @@
         </is>
       </c>
       <c r="D38" s="4">
+        <v>12</v>
+      </c>
+      <c r="E38" s="4">
         <v>3</v>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2718,9 +2835,12 @@
         </is>
       </c>
       <c r="D39" s="4">
+        <v>12</v>
+      </c>
+      <c r="E39" s="4">
         <v>4</v>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2774,9 +2894,12 @@
         </is>
       </c>
       <c r="D40" s="4">
+        <v>12</v>
+      </c>
+      <c r="E40" s="4">
         <v>5</v>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2830,9 +2953,12 @@
         </is>
       </c>
       <c r="D41" s="4">
+        <v>2</v>
+      </c>
+      <c r="E41" s="4">
         <v>1</v>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2860,7 +2986,10 @@
       <c r="D42" s="4">
         <v>1</v>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="E42" s="4">
+        <v>1</v>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2938,7 +3067,10 @@
       <c r="D43" s="4">
         <v>1</v>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E43" s="4">
+        <v>1</v>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2966,7 +3098,10 @@
       <c r="D44" s="4">
         <v>1</v>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="E44" s="4">
+        <v>1</v>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2994,7 +3129,10 @@
       <c r="D45" s="4">
         <v>1</v>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E45" s="4">
+        <v>1</v>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3087,7 +3225,10 @@
       <c r="D46" s="4">
         <v>1</v>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E46" s="4">
+        <v>1</v>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3113,9 +3254,12 @@
         </is>
       </c>
       <c r="D47" s="4">
+        <v>9</v>
+      </c>
+      <c r="E47" s="4">
         <v>1</v>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3169,9 +3313,12 @@
         </is>
       </c>
       <c r="D48" s="4">
+        <v>9</v>
+      </c>
+      <c r="E48" s="4">
         <v>2</v>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3225,9 +3372,12 @@
         </is>
       </c>
       <c r="D49" s="4">
+        <v>9</v>
+      </c>
+      <c r="E49" s="4">
         <v>3</v>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3281,9 +3431,12 @@
         </is>
       </c>
       <c r="D50" s="4">
+        <v>9</v>
+      </c>
+      <c r="E50" s="4">
         <v>4</v>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3339,7 +3492,10 @@
       <c r="D51" s="4">
         <v>1</v>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E51" s="4">
+        <v>1</v>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3365,9 +3521,12 @@
         </is>
       </c>
       <c r="D52" s="4">
+        <v>2</v>
+      </c>
+      <c r="E52" s="4">
         <v>1</v>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3423,7 +3582,10 @@
       <c r="D53" s="4">
         <v>2</v>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="E53" s="4">
+        <v>2</v>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3477,9 +3639,12 @@
         </is>
       </c>
       <c r="D54" s="4">
+        <v>3</v>
+      </c>
+      <c r="E54" s="4">
         <v>1</v>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3540,9 +3705,12 @@
         </is>
       </c>
       <c r="D55" s="4">
+        <v>3</v>
+      </c>
+      <c r="E55" s="4">
         <v>2</v>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3603,9 +3771,12 @@
         </is>
       </c>
       <c r="D56" s="4">
+        <v>3</v>
+      </c>
+      <c r="E56" s="4">
         <v>1</v>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3674,9 +3845,12 @@
         </is>
       </c>
       <c r="D57" s="4">
+        <v>3</v>
+      </c>
+      <c r="E57" s="4">
         <v>2</v>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3747,7 +3921,10 @@
       <c r="D58" s="4">
         <v>1</v>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="E58" s="4">
+        <v>1</v>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3816,9 +3993,12 @@
         </is>
       </c>
       <c r="D59" s="4">
+        <v>3</v>
+      </c>
+      <c r="E59" s="4">
         <v>1</v>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3896,7 +4076,10 @@
       <c r="D60" s="4">
         <v>1</v>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="E60" s="4">
+        <v>1</v>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3974,7 +4157,10 @@
       <c r="D61" s="4">
         <v>1</v>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="E61" s="4">
+        <v>1</v>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4050,9 +4236,12 @@
         </is>
       </c>
       <c r="D62" s="4">
+        <v>3</v>
+      </c>
+      <c r="E62" s="4">
         <v>1</v>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="F62" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4136,9 +4325,12 @@
         </is>
       </c>
       <c r="D63" s="4">
+        <v>3</v>
+      </c>
+      <c r="E63" s="4">
         <v>2</v>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4222,9 +4414,12 @@
         </is>
       </c>
       <c r="D64" s="4">
+        <v>5</v>
+      </c>
+      <c r="E64" s="4">
         <v>1</v>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="F64" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4308,9 +4503,12 @@
         </is>
       </c>
       <c r="D65" s="4">
+        <v>5</v>
+      </c>
+      <c r="E65" s="4">
         <v>2</v>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4394,9 +4592,12 @@
         </is>
       </c>
       <c r="D66" s="4">
+        <v>5</v>
+      </c>
+      <c r="E66" s="4">
         <v>3</v>
       </c>
-      <c r="E66" s="6" t="inlineStr">
+      <c r="F66" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4480,9 +4681,12 @@
         </is>
       </c>
       <c r="D67" s="4">
+        <v>5</v>
+      </c>
+      <c r="E67" s="4">
         <v>4</v>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4566,9 +4770,12 @@
         </is>
       </c>
       <c r="D68" s="4">
+        <v>2</v>
+      </c>
+      <c r="E68" s="4">
         <v>1</v>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="F68" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4659,9 +4866,12 @@
         </is>
       </c>
       <c r="D69" s="4">
+        <v>3</v>
+      </c>
+      <c r="E69" s="4">
         <v>1</v>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4760,9 +4970,12 @@
         </is>
       </c>
       <c r="D70" s="4">
+        <v>3</v>
+      </c>
+      <c r="E70" s="4">
         <v>2</v>
       </c>
-      <c r="E70" s="6" t="inlineStr">
+      <c r="F70" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4861,9 +5074,12 @@
         </is>
       </c>
       <c r="D71" s="4">
+        <v>6</v>
+      </c>
+      <c r="E71" s="4">
         <v>1</v>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4962,9 +5178,12 @@
         </is>
       </c>
       <c r="D72" s="4">
+        <v>6</v>
+      </c>
+      <c r="E72" s="4">
         <v>2</v>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5063,9 +5282,12 @@
         </is>
       </c>
       <c r="D73" s="4">
+        <v>6</v>
+      </c>
+      <c r="E73" s="4">
         <v>3</v>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5166,7 +5388,10 @@
       <c r="D74" s="4">
         <v>1</v>
       </c>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="E74" s="4">
+        <v>1</v>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5272,9 +5497,12 @@
         </is>
       </c>
       <c r="D75" s="4">
+        <v>2</v>
+      </c>
+      <c r="E75" s="4">
         <v>1</v>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5300,9 +5528,12 @@
         </is>
       </c>
       <c r="D76" s="4">
+        <v>3</v>
+      </c>
+      <c r="E76" s="4">
         <v>1</v>
       </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5418,7 +5649,10 @@
       <c r="D77" s="4">
         <v>1</v>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="E77" s="4">
+        <v>1</v>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5532,9 +5766,12 @@
         </is>
       </c>
       <c r="D78" s="4">
+        <v>3</v>
+      </c>
+      <c r="E78" s="4">
         <v>1</v>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="F78" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5648,9 +5885,12 @@
         </is>
       </c>
       <c r="D79" s="4">
+        <v>3</v>
+      </c>
+      <c r="E79" s="4">
         <v>2</v>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5766,7 +6006,10 @@
       <c r="D80" s="4">
         <v>3</v>
       </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="E80" s="4">
+        <v>3</v>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5880,9 +6123,12 @@
         </is>
       </c>
       <c r="D81" s="4">
+        <v>2</v>
+      </c>
+      <c r="E81" s="4">
         <v>1</v>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5936,9 +6182,12 @@
         </is>
       </c>
       <c r="D82" s="4">
+        <v>2</v>
+      </c>
+      <c r="E82" s="4">
         <v>1</v>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="F82" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5964,9 +6213,12 @@
         </is>
       </c>
       <c r="D83" s="4">
+        <v>6</v>
+      </c>
+      <c r="E83" s="4">
         <v>1</v>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6020,9 +6272,12 @@
         </is>
       </c>
       <c r="D84" s="4">
+        <v>6</v>
+      </c>
+      <c r="E84" s="4">
         <v>2</v>
       </c>
-      <c r="E84" s="6" t="inlineStr">
+      <c r="F84" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6076,9 +6331,12 @@
         </is>
       </c>
       <c r="D85" s="4">
+        <v>6</v>
+      </c>
+      <c r="E85" s="4">
         <v>3</v>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6132,9 +6390,12 @@
         </is>
       </c>
       <c r="D86" s="4">
+        <v>6</v>
+      </c>
+      <c r="E86" s="4">
         <v>4</v>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6188,9 +6449,12 @@
         </is>
       </c>
       <c r="D87" s="4">
+        <v>5</v>
+      </c>
+      <c r="E87" s="4">
         <v>1</v>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6251,9 +6515,12 @@
         </is>
       </c>
       <c r="D88" s="4">
+        <v>5</v>
+      </c>
+      <c r="E88" s="4">
         <v>2</v>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6314,9 +6581,12 @@
         </is>
       </c>
       <c r="D89" s="4">
+        <v>2</v>
+      </c>
+      <c r="E89" s="4">
         <v>1</v>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6342,9 +6612,12 @@
         </is>
       </c>
       <c r="D90" s="4">
+        <v>3</v>
+      </c>
+      <c r="E90" s="4">
         <v>1</v>
       </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6405,9 +6678,12 @@
         </is>
       </c>
       <c r="D91" s="4">
+        <v>3</v>
+      </c>
+      <c r="E91" s="4">
         <v>1</v>
       </c>
-      <c r="E91" s="6" t="inlineStr">
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6476,9 +6752,12 @@
         </is>
       </c>
       <c r="D92" s="4">
+        <v>3</v>
+      </c>
+      <c r="E92" s="4">
         <v>2</v>
       </c>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="F92" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6547,9 +6826,12 @@
         </is>
       </c>
       <c r="D93" s="4">
+        <v>2</v>
+      </c>
+      <c r="E93" s="4">
         <v>1</v>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6575,9 +6857,12 @@
         </is>
       </c>
       <c r="D94" s="4">
+        <v>3</v>
+      </c>
+      <c r="E94" s="4">
         <v>1</v>
       </c>
-      <c r="E94" s="6" t="inlineStr">
+      <c r="F94" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6603,9 +6888,12 @@
         </is>
       </c>
       <c r="D95" s="4">
+        <v>2</v>
+      </c>
+      <c r="E95" s="4">
         <v>1</v>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6683,7 +6971,10 @@
       <c r="D96" s="4">
         <v>2</v>
       </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="E96" s="4">
+        <v>2</v>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6761,7 +7052,10 @@
       <c r="D97" s="4">
         <v>1</v>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="E97" s="4">
+        <v>1</v>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6787,9 +7081,12 @@
         </is>
       </c>
       <c r="D98" s="4">
+        <v>2</v>
+      </c>
+      <c r="E98" s="4">
         <v>1</v>
       </c>
-      <c r="E98" s="6" t="inlineStr">
+      <c r="F98" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6875,7 +7172,10 @@
       <c r="D99" s="4">
         <v>1</v>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="E99" s="4">
+        <v>1</v>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6961,7 +7261,10 @@
       <c r="D100" s="4">
         <v>1</v>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="E100" s="4">
+        <v>1</v>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7054,7 +7357,10 @@
       <c r="D101" s="4">
         <v>1</v>
       </c>
-      <c r="E101" s="6" t="inlineStr">
+      <c r="E101" s="4">
+        <v>1</v>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7145,9 +7451,12 @@
         </is>
       </c>
       <c r="D102" s="4">
+        <v>2</v>
+      </c>
+      <c r="E102" s="4">
         <v>1</v>
       </c>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="F102" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7248,7 +7557,10 @@
       <c r="D103" s="4">
         <v>1</v>
       </c>
-      <c r="E103" s="6" t="inlineStr">
+      <c r="E103" s="4">
+        <v>1</v>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7349,7 +7661,10 @@
       <c r="D104" s="4">
         <v>1</v>
       </c>
-      <c r="E104" s="6" t="inlineStr">
+      <c r="E104" s="4">
+        <v>1</v>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7455,9 +7770,12 @@
         </is>
       </c>
       <c r="D105" s="4">
+        <v>2</v>
+      </c>
+      <c r="E105" s="4">
         <v>1</v>
       </c>
-      <c r="E105" s="6" t="inlineStr">
+      <c r="F105" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7565,7 +7883,10 @@
       <c r="D106" s="4">
         <v>1</v>
       </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="E106" s="4">
+        <v>1</v>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7671,9 +7992,12 @@
         </is>
       </c>
       <c r="D107" s="4">
+        <v>4</v>
+      </c>
+      <c r="E107" s="4">
         <v>1</v>
       </c>
-      <c r="E107" s="6" t="inlineStr">
+      <c r="F107" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7787,9 +8111,12 @@
         </is>
       </c>
       <c r="D108" s="4">
+        <v>4</v>
+      </c>
+      <c r="E108" s="4">
         <v>2</v>
       </c>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="F108" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7903,9 +8230,12 @@
         </is>
       </c>
       <c r="D109" s="4">
+        <v>4</v>
+      </c>
+      <c r="E109" s="4">
         <v>3</v>
       </c>
-      <c r="E109" s="6" t="inlineStr">
+      <c r="F109" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8021,7 +8351,10 @@
       <c r="D110" s="4">
         <v>1</v>
       </c>
-      <c r="E110" s="6" t="inlineStr">
+      <c r="E110" s="4">
+        <v>1</v>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8075,9 +8408,12 @@
         </is>
       </c>
       <c r="D111" s="4">
+        <v>2</v>
+      </c>
+      <c r="E111" s="4">
         <v>1</v>
       </c>
-      <c r="E111" s="6" t="inlineStr">
+      <c r="F111" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8105,7 +8441,10 @@
       <c r="D112" s="4">
         <v>1</v>
       </c>
-      <c r="E112" s="6" t="inlineStr">
+      <c r="E112" s="4">
+        <v>1</v>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8161,7 +8500,10 @@
       <c r="D113" s="4">
         <v>1</v>
       </c>
-      <c r="E113" s="6" t="inlineStr">
+      <c r="E113" s="4">
+        <v>1</v>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8187,9 +8529,12 @@
         </is>
       </c>
       <c r="D114" s="4">
+        <v>2</v>
+      </c>
+      <c r="E114" s="4">
         <v>1</v>
       </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="F114" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8217,7 +8562,10 @@
       <c r="D115" s="4">
         <v>1</v>
       </c>
-      <c r="E115" s="6" t="inlineStr">
+      <c r="E115" s="4">
+        <v>1</v>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8288,7 +8636,10 @@
       <c r="D116" s="4">
         <v>1</v>
       </c>
-      <c r="E116" s="6" t="inlineStr">
+      <c r="E116" s="4">
+        <v>1</v>
+      </c>
+      <c r="F116" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8357,9 +8708,12 @@
         </is>
       </c>
       <c r="D117" s="4">
+        <v>3</v>
+      </c>
+      <c r="E117" s="4">
         <v>1</v>
       </c>
-      <c r="E117" s="6" t="inlineStr">
+      <c r="F117" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8435,9 +8789,12 @@
         </is>
       </c>
       <c r="D118" s="4">
+        <v>3</v>
+      </c>
+      <c r="E118" s="4">
         <v>2</v>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="F118" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8515,7 +8872,10 @@
       <c r="D119" s="4">
         <v>1</v>
       </c>
-      <c r="E119" s="6" t="inlineStr">
+      <c r="E119" s="4">
+        <v>1</v>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8541,9 +8901,12 @@
         </is>
       </c>
       <c r="D120" s="4">
+        <v>2</v>
+      </c>
+      <c r="E120" s="4">
         <v>1</v>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="F120" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8627,9 +8990,12 @@
         </is>
       </c>
       <c r="D121" s="4">
+        <v>3</v>
+      </c>
+      <c r="E121" s="4">
         <v>1</v>
       </c>
-      <c r="E121" s="6" t="inlineStr">
+      <c r="F121" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8713,9 +9079,12 @@
         </is>
       </c>
       <c r="D122" s="4">
+        <v>3</v>
+      </c>
+      <c r="E122" s="4">
         <v>2</v>
       </c>
-      <c r="E122" s="6" t="inlineStr">
+      <c r="F122" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8801,7 +9170,10 @@
       <c r="D123" s="4">
         <v>1</v>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="E123" s="4">
+        <v>1</v>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8887,7 +9259,10 @@
       <c r="D124" s="4">
         <v>1</v>
       </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="E124" s="4">
+        <v>1</v>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8915,7 +9290,10 @@
       <c r="D125" s="4">
         <v>1</v>
       </c>
-      <c r="E125" s="6" t="inlineStr">
+      <c r="E125" s="4">
+        <v>1</v>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8943,7 +9321,10 @@
       <c r="D126" s="4">
         <v>1</v>
       </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="E126" s="4">
+        <v>1</v>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8969,9 +9350,12 @@
         </is>
       </c>
       <c r="D127" s="4">
+        <v>2</v>
+      </c>
+      <c r="E127" s="4">
         <v>1</v>
       </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="F127" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9072,7 +9456,10 @@
       <c r="D128" s="4">
         <v>1</v>
       </c>
-      <c r="E128" s="6" t="inlineStr">
+      <c r="E128" s="4">
+        <v>1</v>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9180,7 +9567,10 @@
       <c r="D129" s="4">
         <v>1</v>
       </c>
-      <c r="E129" s="6" t="inlineStr">
+      <c r="E129" s="4">
+        <v>1</v>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9206,9 +9596,12 @@
         </is>
       </c>
       <c r="D130" s="4">
+        <v>2</v>
+      </c>
+      <c r="E130" s="4">
         <v>1</v>
       </c>
-      <c r="E130" s="6" t="inlineStr">
+      <c r="F130" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9236,7 +9629,10 @@
       <c r="D131" s="4">
         <v>1</v>
       </c>
-      <c r="E131" s="6" t="inlineStr">
+      <c r="E131" s="4">
+        <v>1</v>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9299,7 +9695,10 @@
       <c r="D132" s="4">
         <v>1</v>
       </c>
-      <c r="E132" s="6" t="inlineStr">
+      <c r="E132" s="4">
+        <v>1</v>
+      </c>
+      <c r="F132" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9325,9 +9724,12 @@
         </is>
       </c>
       <c r="D133" s="4">
+        <v>2</v>
+      </c>
+      <c r="E133" s="4">
         <v>1</v>
       </c>
-      <c r="E133" s="6" t="inlineStr">
+      <c r="F133" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9398,7 +9800,10 @@
       <c r="D134" s="4">
         <v>1</v>
       </c>
-      <c r="E134" s="6" t="inlineStr">
+      <c r="E134" s="4">
+        <v>1</v>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9476,7 +9881,10 @@
       <c r="D135" s="4">
         <v>1</v>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="E135" s="4">
+        <v>1</v>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9504,7 +9912,10 @@
       <c r="D136" s="4">
         <v>1</v>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="E136" s="4">
+        <v>1</v>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9610,9 +10021,12 @@
         </is>
       </c>
       <c r="D137" s="4">
+        <v>2</v>
+      </c>
+      <c r="E137" s="4">
         <v>1</v>
       </c>
-      <c r="E137" s="6" t="inlineStr">
+      <c r="F137" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9666,9 +10080,12 @@
         </is>
       </c>
       <c r="D138" s="4">
+        <v>4</v>
+      </c>
+      <c r="E138" s="4">
         <v>1</v>
       </c>
-      <c r="E138" s="6" t="inlineStr">
+      <c r="F138" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9722,9 +10139,12 @@
         </is>
       </c>
       <c r="D139" s="4">
+        <v>4</v>
+      </c>
+      <c r="E139" s="4">
         <v>2</v>
       </c>
-      <c r="E139" s="6" t="inlineStr">
+      <c r="F139" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9778,9 +10198,12 @@
         </is>
       </c>
       <c r="D140" s="4">
+        <v>4</v>
+      </c>
+      <c r="E140" s="4">
         <v>3</v>
       </c>
-      <c r="E140" s="6" t="inlineStr">
+      <c r="F140" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9834,9 +10257,12 @@
         </is>
       </c>
       <c r="D141" s="4">
+        <v>2</v>
+      </c>
+      <c r="E141" s="4">
         <v>1</v>
       </c>
-      <c r="E141" s="6" t="inlineStr">
+      <c r="F141" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9907,7 +10333,10 @@
       <c r="D142" s="4">
         <v>2</v>
       </c>
-      <c r="E142" s="6" t="inlineStr">
+      <c r="E142" s="4">
+        <v>2</v>
+      </c>
+      <c r="F142" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9978,7 +10407,10 @@
       <c r="D143" s="4">
         <v>1</v>
       </c>
-      <c r="E143" s="6" t="inlineStr">
+      <c r="E143" s="4">
+        <v>1</v>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10062,9 +10494,12 @@
         </is>
       </c>
       <c r="D144" s="4">
+        <v>2</v>
+      </c>
+      <c r="E144" s="4">
         <v>1</v>
       </c>
-      <c r="E144" s="6" t="inlineStr">
+      <c r="F144" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10092,7 +10527,10 @@
       <c r="D145" s="4">
         <v>1</v>
       </c>
-      <c r="E145" s="6" t="inlineStr">
+      <c r="E145" s="4">
+        <v>1</v>
+      </c>
+      <c r="F145" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10120,7 +10558,10 @@
       <c r="D146" s="4">
         <v>1</v>
       </c>
-      <c r="E146" s="6" t="inlineStr">
+      <c r="E146" s="4">
+        <v>1</v>
+      </c>
+      <c r="F146" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10148,7 +10589,10 @@
       <c r="D147" s="4">
         <v>1</v>
       </c>
-      <c r="E147" s="6" t="inlineStr">
+      <c r="E147" s="4">
+        <v>1</v>
+      </c>
+      <c r="F147" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10176,7 +10620,10 @@
       <c r="D148" s="4">
         <v>1</v>
       </c>
-      <c r="E148" s="6" t="inlineStr">
+      <c r="E148" s="4">
+        <v>1</v>
+      </c>
+      <c r="F148" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10230,9 +10677,12 @@
         </is>
       </c>
       <c r="D149" s="4">
+        <v>3</v>
+      </c>
+      <c r="E149" s="4">
         <v>1</v>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="F149" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10260,7 +10710,10 @@
       <c r="D150" s="4">
         <v>1</v>
       </c>
-      <c r="E150" s="6" t="inlineStr">
+      <c r="E150" s="4">
+        <v>1</v>
+      </c>
+      <c r="F150" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10288,7 +10741,10 @@
       <c r="D151" s="4">
         <v>1</v>
       </c>
-      <c r="E151" s="6" t="inlineStr">
+      <c r="E151" s="4">
+        <v>1</v>
+      </c>
+      <c r="F151" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -10314,9 +10770,12 @@
         </is>
       </c>
       <c r="D152" s="4">
+        <v>2</v>
+      </c>
+      <c r="E152" s="4">
         <v>1</v>
       </c>
-      <c r="E152" s="6" t="inlineStr">
+      <c r="F152" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10415,9 +10874,12 @@
         </is>
       </c>
       <c r="D153" s="4">
+        <v>2</v>
+      </c>
+      <c r="E153" s="4">
         <v>1</v>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="F153" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10525,7 +10987,10 @@
       <c r="D154" s="4">
         <v>1</v>
       </c>
-      <c r="E154" s="6" t="inlineStr">
+      <c r="E154" s="4">
+        <v>1</v>
+      </c>
+      <c r="F154" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10631,9 +11096,12 @@
         </is>
       </c>
       <c r="D155" s="4">
+        <v>2</v>
+      </c>
+      <c r="E155" s="4">
         <v>1</v>
       </c>
-      <c r="E155" s="6" t="inlineStr">
+      <c r="F155" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10756,7 +11224,10 @@
       <c r="D156" s="4">
         <v>1</v>
       </c>
-      <c r="E156" s="6" t="inlineStr">
+      <c r="E156" s="4">
+        <v>1</v>
+      </c>
+      <c r="F156" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10812,7 +11283,10 @@
       <c r="D157" s="4">
         <v>1</v>
       </c>
-      <c r="E157" s="6" t="inlineStr">
+      <c r="E157" s="4">
+        <v>1</v>
+      </c>
+      <c r="F157" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10866,9 +11340,12 @@
         </is>
       </c>
       <c r="D158" s="4">
+        <v>2</v>
+      </c>
+      <c r="E158" s="4">
         <v>1</v>
       </c>
-      <c r="E158" s="6" t="inlineStr">
+      <c r="F158" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10929,9 +11406,12 @@
         </is>
       </c>
       <c r="D159" s="4">
+        <v>3</v>
+      </c>
+      <c r="E159" s="4">
         <v>1</v>
       </c>
-      <c r="E159" s="6" t="inlineStr">
+      <c r="F159" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11007,9 +11487,12 @@
         </is>
       </c>
       <c r="D160" s="4">
+        <v>3</v>
+      </c>
+      <c r="E160" s="4">
         <v>2</v>
       </c>
-      <c r="E160" s="6" t="inlineStr">
+      <c r="F160" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11087,7 +11570,10 @@
       <c r="D161" s="4">
         <v>1</v>
       </c>
-      <c r="E161" s="6" t="inlineStr">
+      <c r="E161" s="4">
+        <v>1</v>
+      </c>
+      <c r="F161" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -11115,7 +11601,10 @@
       <c r="D162" s="4">
         <v>1</v>
       </c>
-      <c r="E162" s="6" t="inlineStr">
+      <c r="E162" s="4">
+        <v>1</v>
+      </c>
+      <c r="F162" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11201,7 +11690,10 @@
       <c r="D163" s="4">
         <v>1</v>
       </c>
-      <c r="E163" s="6" t="inlineStr">
+      <c r="E163" s="4">
+        <v>1</v>
+      </c>
+      <c r="F163" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -11229,7 +11721,10 @@
       <c r="D164" s="4">
         <v>1</v>
       </c>
-      <c r="E164" s="6" t="inlineStr">
+      <c r="E164" s="4">
+        <v>1</v>
+      </c>
+      <c r="F164" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11335,9 +11830,12 @@
         </is>
       </c>
       <c r="D165" s="4">
+        <v>3</v>
+      </c>
+      <c r="E165" s="4">
         <v>1</v>
       </c>
-      <c r="E165" s="6" t="inlineStr">
+      <c r="F165" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11451,9 +11949,12 @@
         </is>
       </c>
       <c r="D166" s="4">
+        <v>3</v>
+      </c>
+      <c r="E166" s="4">
         <v>2</v>
       </c>
-      <c r="E166" s="6" t="inlineStr">
+      <c r="F166" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11569,7 +12070,10 @@
       <c r="D167" s="4">
         <v>1</v>
       </c>
-      <c r="E167" s="6" t="inlineStr">
+      <c r="E167" s="4">
+        <v>1</v>
+      </c>
+      <c r="F167" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11690,9 +12194,12 @@
         </is>
       </c>
       <c r="D168" s="4">
+        <v>2</v>
+      </c>
+      <c r="E168" s="4">
         <v>1</v>
       </c>
-      <c r="E168" s="6" t="inlineStr">
+      <c r="F168" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11815,7 +12322,10 @@
       <c r="D169" s="4">
         <v>2</v>
       </c>
-      <c r="E169" s="6" t="inlineStr">
+      <c r="E169" s="4">
+        <v>2</v>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11938,7 +12448,10 @@
       <c r="D170" s="4">
         <v>1</v>
       </c>
-      <c r="E170" s="6" t="inlineStr">
+      <c r="E170" s="4">
+        <v>1</v>
+      </c>
+      <c r="F170" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -11964,9 +12477,12 @@
         </is>
       </c>
       <c r="D171" s="4">
+        <v>2</v>
+      </c>
+      <c r="E171" s="4">
         <v>1</v>
       </c>
-      <c r="E171" s="6" t="inlineStr">
+      <c r="F171" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12020,9 +12536,12 @@
         </is>
       </c>
       <c r="D172" s="4">
+        <v>3</v>
+      </c>
+      <c r="E172" s="4">
         <v>1</v>
       </c>
-      <c r="E172" s="6" t="inlineStr">
+      <c r="F172" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -12050,7 +12569,10 @@
       <c r="D173" s="4">
         <v>1</v>
       </c>
-      <c r="E173" s="6" t="inlineStr">
+      <c r="E173" s="4">
+        <v>1</v>
+      </c>
+      <c r="F173" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -12078,7 +12600,10 @@
       <c r="D174" s="4">
         <v>1</v>
       </c>
-      <c r="E174" s="6" t="inlineStr">
+      <c r="E174" s="4">
+        <v>1</v>
+      </c>
+      <c r="F174" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12154,9 +12679,12 @@
         </is>
       </c>
       <c r="D175" s="4">
+        <v>2</v>
+      </c>
+      <c r="E175" s="4">
         <v>1</v>
       </c>
-      <c r="E175" s="6" t="inlineStr">
+      <c r="F175" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12242,7 +12770,10 @@
       <c r="D176" s="4">
         <v>2</v>
       </c>
-      <c r="E176" s="6" t="inlineStr">
+      <c r="E176" s="4">
+        <v>2</v>
+      </c>
+      <c r="F176" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12328,7 +12859,10 @@
       <c r="D177" s="4">
         <v>1</v>
       </c>
-      <c r="E177" s="6" t="inlineStr">
+      <c r="E177" s="4">
+        <v>1</v>
+      </c>
+      <c r="F177" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -12356,7 +12890,10 @@
       <c r="D178" s="4">
         <v>1</v>
       </c>
-      <c r="E178" s="6" t="inlineStr">
+      <c r="E178" s="4">
+        <v>1</v>
+      </c>
+      <c r="F178" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12464,7 +13001,10 @@
       <c r="D179" s="4">
         <v>1</v>
       </c>
-      <c r="E179" s="6" t="inlineStr">
+      <c r="E179" s="4">
+        <v>1</v>
+      </c>
+      <c r="F179" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12578,9 +13118,12 @@
         </is>
       </c>
       <c r="D180" s="4">
+        <v>2</v>
+      </c>
+      <c r="E180" s="4">
         <v>1</v>
       </c>
-      <c r="E180" s="6" t="inlineStr">
+      <c r="F180" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12701,9 +13244,12 @@
         </is>
       </c>
       <c r="D181" s="4">
+        <v>4</v>
+      </c>
+      <c r="E181" s="4">
         <v>1</v>
       </c>
-      <c r="E181" s="6" t="inlineStr">
+      <c r="F181" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12757,9 +13303,12 @@
         </is>
       </c>
       <c r="D182" s="4">
+        <v>4</v>
+      </c>
+      <c r="E182" s="4">
         <v>2</v>
       </c>
-      <c r="E182" s="6" t="inlineStr">
+      <c r="F182" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12813,9 +13362,12 @@
         </is>
       </c>
       <c r="D183" s="4">
+        <v>4</v>
+      </c>
+      <c r="E183" s="4">
         <v>3</v>
       </c>
-      <c r="E183" s="6" t="inlineStr">
+      <c r="F183" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12871,7 +13423,10 @@
       <c r="D184" s="4">
         <v>4</v>
       </c>
-      <c r="E184" s="6" t="inlineStr">
+      <c r="E184" s="4">
+        <v>4</v>
+      </c>
+      <c r="F184" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12927,7 +13482,10 @@
       <c r="D185" s="4">
         <v>1</v>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="E185" s="4">
+        <v>1</v>
+      </c>
+      <c r="F185" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12981,9 +13539,12 @@
         </is>
       </c>
       <c r="D186" s="4">
+        <v>4</v>
+      </c>
+      <c r="E186" s="4">
         <v>1</v>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="F186" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13037,9 +13598,12 @@
         </is>
       </c>
       <c r="D187" s="4">
+        <v>4</v>
+      </c>
+      <c r="E187" s="4">
         <v>2</v>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="F187" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13093,9 +13657,12 @@
         </is>
       </c>
       <c r="D188" s="4">
+        <v>4</v>
+      </c>
+      <c r="E188" s="4">
         <v>3</v>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="F188" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13151,7 +13718,10 @@
       <c r="D189" s="4">
         <v>4</v>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="E189" s="4">
+        <v>4</v>
+      </c>
+      <c r="F189" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13205,9 +13775,12 @@
         </is>
       </c>
       <c r="D190" s="4">
+        <v>2</v>
+      </c>
+      <c r="E190" s="4">
         <v>1</v>
       </c>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="F190" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13263,7 +13836,10 @@
       <c r="D191" s="4">
         <v>2</v>
       </c>
-      <c r="E191" s="6" t="inlineStr">
+      <c r="E191" s="4">
+        <v>2</v>
+      </c>
+      <c r="F191" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13317,9 +13893,12 @@
         </is>
       </c>
       <c r="D192" s="4">
+        <v>2</v>
+      </c>
+      <c r="E192" s="4">
         <v>1</v>
       </c>
-      <c r="E192" s="6" t="inlineStr">
+      <c r="F192" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13375,7 +13954,10 @@
       <c r="D193" s="4">
         <v>2</v>
       </c>
-      <c r="E193" s="6" t="inlineStr">
+      <c r="E193" s="4">
+        <v>2</v>
+      </c>
+      <c r="F193" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13429,9 +14011,12 @@
         </is>
       </c>
       <c r="D194" s="4">
+        <v>2</v>
+      </c>
+      <c r="E194" s="4">
         <v>1</v>
       </c>
-      <c r="E194" s="6" t="inlineStr">
+      <c r="F194" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13487,7 +14072,10 @@
       <c r="D195" s="4">
         <v>2</v>
       </c>
-      <c r="E195" s="6" t="inlineStr">
+      <c r="E195" s="4">
+        <v>2</v>
+      </c>
+      <c r="F195" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13541,9 +14129,12 @@
         </is>
       </c>
       <c r="D196" s="4">
+        <v>12</v>
+      </c>
+      <c r="E196" s="4">
         <v>1</v>
       </c>
-      <c r="E196" s="6" t="inlineStr">
+      <c r="F196" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13597,9 +14188,12 @@
         </is>
       </c>
       <c r="D197" s="4">
+        <v>12</v>
+      </c>
+      <c r="E197" s="4">
         <v>2</v>
       </c>
-      <c r="E197" s="6" t="inlineStr">
+      <c r="F197" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13653,9 +14247,12 @@
         </is>
       </c>
       <c r="D198" s="4">
+        <v>12</v>
+      </c>
+      <c r="E198" s="4">
         <v>3</v>
       </c>
-      <c r="E198" s="6" t="inlineStr">
+      <c r="F198" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13709,9 +14306,12 @@
         </is>
       </c>
       <c r="D199" s="4">
+        <v>12</v>
+      </c>
+      <c r="E199" s="4">
         <v>4</v>
       </c>
-      <c r="E199" s="6" t="inlineStr">
+      <c r="F199" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13765,9 +14365,12 @@
         </is>
       </c>
       <c r="D200" s="4">
+        <v>12</v>
+      </c>
+      <c r="E200" s="4">
         <v>5</v>
       </c>
-      <c r="E200" s="6" t="inlineStr">
+      <c r="F200" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13821,9 +14424,12 @@
         </is>
       </c>
       <c r="D201" s="4">
+        <v>12</v>
+      </c>
+      <c r="E201" s="4">
         <v>6</v>
       </c>
-      <c r="E201" s="6" t="inlineStr">
+      <c r="F201" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13877,9 +14483,12 @@
         </is>
       </c>
       <c r="D202" s="4">
+        <v>12</v>
+      </c>
+      <c r="E202" s="4">
         <v>7</v>
       </c>
-      <c r="E202" s="6" t="inlineStr">
+      <c r="F202" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13933,9 +14542,12 @@
         </is>
       </c>
       <c r="D203" s="4">
+        <v>12</v>
+      </c>
+      <c r="E203" s="4">
         <v>8</v>
       </c>
-      <c r="E203" s="6" t="inlineStr">
+      <c r="F203" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13989,9 +14601,12 @@
         </is>
       </c>
       <c r="D204" s="4">
+        <v>12</v>
+      </c>
+      <c r="E204" s="4">
         <v>9</v>
       </c>
-      <c r="E204" s="6" t="inlineStr">
+      <c r="F204" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14045,9 +14660,12 @@
         </is>
       </c>
       <c r="D205" s="4">
+        <v>12</v>
+      </c>
+      <c r="E205" s="4">
         <v>10</v>
       </c>
-      <c r="E205" s="6" t="inlineStr">
+      <c r="F205" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14101,9 +14719,12 @@
         </is>
       </c>
       <c r="D206" s="4">
+        <v>12</v>
+      </c>
+      <c r="E206" s="4">
         <v>11</v>
       </c>
-      <c r="E206" s="6" t="inlineStr">
+      <c r="F206" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14159,7 +14780,10 @@
       <c r="D207" s="4">
         <v>12</v>
       </c>
-      <c r="E207" s="6" t="inlineStr">
+      <c r="E207" s="4">
+        <v>12</v>
+      </c>
+      <c r="F207" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14213,9 +14837,12 @@
         </is>
       </c>
       <c r="D208" s="4">
+        <v>5</v>
+      </c>
+      <c r="E208" s="4">
         <v>1</v>
       </c>
-      <c r="E208" s="6" t="inlineStr">
+      <c r="F208" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14269,9 +14896,12 @@
         </is>
       </c>
       <c r="D209" s="4">
+        <v>5</v>
+      </c>
+      <c r="E209" s="4">
         <v>2</v>
       </c>
-      <c r="E209" s="6" t="inlineStr">
+      <c r="F209" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14325,9 +14955,12 @@
         </is>
       </c>
       <c r="D210" s="4">
+        <v>5</v>
+      </c>
+      <c r="E210" s="4">
         <v>3</v>
       </c>
-      <c r="E210" s="6" t="inlineStr">
+      <c r="F210" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14381,9 +15014,12 @@
         </is>
       </c>
       <c r="D211" s="4">
+        <v>5</v>
+      </c>
+      <c r="E211" s="4">
         <v>4</v>
       </c>
-      <c r="E211" s="6" t="inlineStr">
+      <c r="F211" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14439,7 +15075,10 @@
       <c r="D212" s="4">
         <v>5</v>
       </c>
-      <c r="E212" s="6" t="inlineStr">
+      <c r="E212" s="4">
+        <v>5</v>
+      </c>
+      <c r="F212" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14493,9 +15132,12 @@
         </is>
       </c>
       <c r="D213" s="4">
+        <v>4</v>
+      </c>
+      <c r="E213" s="4">
         <v>1</v>
       </c>
-      <c r="E213" s="6" t="inlineStr">
+      <c r="F213" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14549,9 +15191,12 @@
         </is>
       </c>
       <c r="D214" s="4">
+        <v>4</v>
+      </c>
+      <c r="E214" s="4">
         <v>2</v>
       </c>
-      <c r="E214" s="6" t="inlineStr">
+      <c r="F214" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14605,9 +15250,12 @@
         </is>
       </c>
       <c r="D215" s="4">
+        <v>4</v>
+      </c>
+      <c r="E215" s="4">
         <v>3</v>
       </c>
-      <c r="E215" s="6" t="inlineStr">
+      <c r="F215" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14663,7 +15311,10 @@
       <c r="D216" s="4">
         <v>4</v>
       </c>
-      <c r="E216" s="6" t="inlineStr">
+      <c r="E216" s="4">
+        <v>4</v>
+      </c>
+      <c r="F216" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14717,9 +15368,12 @@
         </is>
       </c>
       <c r="D217" s="4">
+        <v>2</v>
+      </c>
+      <c r="E217" s="4">
         <v>1</v>
       </c>
-      <c r="E217" s="6" t="inlineStr">
+      <c r="F217" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14775,7 +15429,10 @@
       <c r="D218" s="4">
         <v>2</v>
       </c>
-      <c r="E218" s="6" t="inlineStr">
+      <c r="E218" s="4">
+        <v>2</v>
+      </c>
+      <c r="F218" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14829,9 +15486,12 @@
         </is>
       </c>
       <c r="D219" s="4">
+        <v>6</v>
+      </c>
+      <c r="E219" s="4">
         <v>1</v>
       </c>
-      <c r="E219" s="6" t="inlineStr">
+      <c r="F219" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14885,9 +15545,12 @@
         </is>
       </c>
       <c r="D220" s="4">
+        <v>6</v>
+      </c>
+      <c r="E220" s="4">
         <v>2</v>
       </c>
-      <c r="E220" s="6" t="inlineStr">
+      <c r="F220" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14941,9 +15604,12 @@
         </is>
       </c>
       <c r="D221" s="4">
+        <v>6</v>
+      </c>
+      <c r="E221" s="4">
         <v>3</v>
       </c>
-      <c r="E221" s="6" t="inlineStr">
+      <c r="F221" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14997,9 +15663,12 @@
         </is>
       </c>
       <c r="D222" s="4">
+        <v>6</v>
+      </c>
+      <c r="E222" s="4">
         <v>4</v>
       </c>
-      <c r="E222" s="6" t="inlineStr">
+      <c r="F222" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15053,9 +15722,12 @@
         </is>
       </c>
       <c r="D223" s="4">
+        <v>6</v>
+      </c>
+      <c r="E223" s="4">
         <v>5</v>
       </c>
-      <c r="E223" s="6" t="inlineStr">
+      <c r="F223" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15111,7 +15783,10 @@
       <c r="D224" s="4">
         <v>6</v>
       </c>
-      <c r="E224" s="6" t="inlineStr">
+      <c r="E224" s="4">
+        <v>6</v>
+      </c>
+      <c r="F224" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15167,7 +15842,10 @@
       <c r="D225" s="4">
         <v>1</v>
       </c>
-      <c r="E225" s="6" t="inlineStr">
+      <c r="E225" s="4">
+        <v>1</v>
+      </c>
+      <c r="F225" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15223,7 +15901,10 @@
       <c r="D226" s="4">
         <v>1</v>
       </c>
-      <c r="E226" s="6" t="inlineStr">
+      <c r="E226" s="4">
+        <v>1</v>
+      </c>
+      <c r="F226" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15279,7 +15960,10 @@
       <c r="D227" s="4">
         <v>1</v>
       </c>
-      <c r="E227" s="6" t="inlineStr">
+      <c r="E227" s="4">
+        <v>1</v>
+      </c>
+      <c r="F227" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15333,9 +16017,12 @@
         </is>
       </c>
       <c r="D228" s="4">
+        <v>4</v>
+      </c>
+      <c r="E228" s="4">
         <v>1</v>
       </c>
-      <c r="E228" s="6" t="inlineStr">
+      <c r="F228" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15389,9 +16076,12 @@
         </is>
       </c>
       <c r="D229" s="4">
+        <v>4</v>
+      </c>
+      <c r="E229" s="4">
         <v>2</v>
       </c>
-      <c r="E229" s="6" t="inlineStr">
+      <c r="F229" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15445,9 +16135,12 @@
         </is>
       </c>
       <c r="D230" s="4">
+        <v>4</v>
+      </c>
+      <c r="E230" s="4">
         <v>3</v>
       </c>
-      <c r="E230" s="6" t="inlineStr">
+      <c r="F230" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15503,7 +16196,10 @@
       <c r="D231" s="4">
         <v>4</v>
       </c>
-      <c r="E231" s="6" t="inlineStr">
+      <c r="E231" s="4">
+        <v>4</v>
+      </c>
+      <c r="F231" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15557,9 +16253,12 @@
         </is>
       </c>
       <c r="D232" s="4">
+        <v>11</v>
+      </c>
+      <c r="E232" s="4">
         <v>1</v>
       </c>
-      <c r="E232" s="6" t="inlineStr">
+      <c r="F232" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15613,9 +16312,12 @@
         </is>
       </c>
       <c r="D233" s="4">
+        <v>11</v>
+      </c>
+      <c r="E233" s="4">
         <v>2</v>
       </c>
-      <c r="E233" s="6" t="inlineStr">
+      <c r="F233" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15669,9 +16371,12 @@
         </is>
       </c>
       <c r="D234" s="4">
+        <v>11</v>
+      </c>
+      <c r="E234" s="4">
         <v>3</v>
       </c>
-      <c r="E234" s="6" t="inlineStr">
+      <c r="F234" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15725,9 +16430,12 @@
         </is>
       </c>
       <c r="D235" s="4">
+        <v>11</v>
+      </c>
+      <c r="E235" s="4">
         <v>4</v>
       </c>
-      <c r="E235" s="6" t="inlineStr">
+      <c r="F235" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15781,9 +16489,12 @@
         </is>
       </c>
       <c r="D236" s="4">
+        <v>11</v>
+      </c>
+      <c r="E236" s="4">
         <v>5</v>
       </c>
-      <c r="E236" s="6" t="inlineStr">
+      <c r="F236" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15837,9 +16548,12 @@
         </is>
       </c>
       <c r="D237" s="4">
+        <v>11</v>
+      </c>
+      <c r="E237" s="4">
         <v>6</v>
       </c>
-      <c r="E237" s="6" t="inlineStr">
+      <c r="F237" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15893,9 +16607,12 @@
         </is>
       </c>
       <c r="D238" s="4">
+        <v>11</v>
+      </c>
+      <c r="E238" s="4">
         <v>7</v>
       </c>
-      <c r="E238" s="6" t="inlineStr">
+      <c r="F238" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15949,9 +16666,12 @@
         </is>
       </c>
       <c r="D239" s="4">
+        <v>11</v>
+      </c>
+      <c r="E239" s="4">
         <v>8</v>
       </c>
-      <c r="E239" s="6" t="inlineStr">
+      <c r="F239" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16005,9 +16725,12 @@
         </is>
       </c>
       <c r="D240" s="4">
+        <v>11</v>
+      </c>
+      <c r="E240" s="4">
         <v>9</v>
       </c>
-      <c r="E240" s="6" t="inlineStr">
+      <c r="F240" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16061,9 +16784,12 @@
         </is>
       </c>
       <c r="D241" s="4">
+        <v>11</v>
+      </c>
+      <c r="E241" s="4">
         <v>10</v>
       </c>
-      <c r="E241" s="6" t="inlineStr">
+      <c r="F241" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16119,7 +16845,10 @@
       <c r="D242" s="4">
         <v>11</v>
       </c>
-      <c r="E242" s="6" t="inlineStr">
+      <c r="E242" s="4">
+        <v>11</v>
+      </c>
+      <c r="F242" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16173,9 +16902,12 @@
         </is>
       </c>
       <c r="D243" s="4">
+        <v>2</v>
+      </c>
+      <c r="E243" s="4">
         <v>1</v>
       </c>
-      <c r="E243" s="6" t="inlineStr">
+      <c r="F243" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16247,7 +16979,10 @@
       <c r="D244" s="4">
         <v>2</v>
       </c>
-      <c r="E244" s="6" t="inlineStr">
+      <c r="E244" s="4">
+        <v>2</v>
+      </c>
+      <c r="F244" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16319,7 +17054,10 @@
       <c r="D245" s="4">
         <v>1</v>
       </c>
-      <c r="E245" s="6" t="inlineStr">
+      <c r="E245" s="4">
+        <v>1</v>
+      </c>
+      <c r="F245" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16380,9 +17118,12 @@
         </is>
       </c>
       <c r="D246" s="4">
+        <v>4</v>
+      </c>
+      <c r="E246" s="4">
         <v>1</v>
       </c>
-      <c r="E246" s="6" t="inlineStr">
+      <c r="F246" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16443,9 +17184,12 @@
         </is>
       </c>
       <c r="D247" s="4">
+        <v>4</v>
+      </c>
+      <c r="E247" s="4">
         <v>2</v>
       </c>
-      <c r="E247" s="6" t="inlineStr">
+      <c r="F247" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16506,9 +17250,12 @@
         </is>
       </c>
       <c r="D248" s="4">
+        <v>4</v>
+      </c>
+      <c r="E248" s="4">
         <v>3</v>
       </c>
-      <c r="E248" s="6" t="inlineStr">
+      <c r="F248" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16594,7 +17341,10 @@
       <c r="D249" s="4">
         <v>4</v>
       </c>
-      <c r="E249" s="6" t="inlineStr">
+      <c r="E249" s="4">
+        <v>4</v>
+      </c>
+      <c r="F249" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16663,9 +17413,12 @@
         </is>
       </c>
       <c r="D250" s="4">
+        <v>3</v>
+      </c>
+      <c r="E250" s="4">
         <v>1</v>
       </c>
-      <c r="E250" s="6" t="inlineStr">
+      <c r="F250" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16726,9 +17479,12 @@
         </is>
       </c>
       <c r="D251" s="4">
+        <v>3</v>
+      </c>
+      <c r="E251" s="4">
         <v>2</v>
       </c>
-      <c r="E251" s="6" t="inlineStr">
+      <c r="F251" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16791,7 +17547,10 @@
       <c r="D252" s="4">
         <v>3</v>
       </c>
-      <c r="E252" s="6" t="inlineStr">
+      <c r="E252" s="4">
+        <v>3</v>
+      </c>
+      <c r="F252" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16854,7 +17613,10 @@
       <c r="D253" s="4">
         <v>1</v>
       </c>
-      <c r="E253" s="6" t="inlineStr">
+      <c r="E253" s="4">
+        <v>1</v>
+      </c>
+      <c r="F253" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16925,7 +17687,10 @@
       <c r="D254" s="4">
         <v>1</v>
       </c>
-      <c r="E254" s="6" t="inlineStr">
+      <c r="E254" s="4">
+        <v>1</v>
+      </c>
+      <c r="F254" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17001,9 +17766,12 @@
         </is>
       </c>
       <c r="D255" s="4">
+        <v>163</v>
+      </c>
+      <c r="E255" s="4">
         <v>1</v>
       </c>
-      <c r="E255" s="6" t="inlineStr">
+      <c r="F255" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17109,9 +17877,12 @@
         </is>
       </c>
       <c r="D256" s="4">
+        <v>163</v>
+      </c>
+      <c r="E256" s="4">
         <v>2</v>
       </c>
-      <c r="E256" s="6" t="inlineStr">
+      <c r="F256" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17225,9 +17996,12 @@
         </is>
       </c>
       <c r="D257" s="4">
+        <v>163</v>
+      </c>
+      <c r="E257" s="4">
         <v>3</v>
       </c>
-      <c r="E257" s="6" t="inlineStr">
+      <c r="F257" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17378,9 +18152,12 @@
         </is>
       </c>
       <c r="D258" s="4">
+        <v>163</v>
+      </c>
+      <c r="E258" s="4">
         <v>4</v>
       </c>
-      <c r="E258" s="6" t="inlineStr">
+      <c r="F258" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17486,9 +18263,12 @@
         </is>
       </c>
       <c r="D259" s="4">
+        <v>163</v>
+      </c>
+      <c r="E259" s="4">
         <v>5</v>
       </c>
-      <c r="E259" s="6" t="inlineStr">
+      <c r="F259" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17624,9 +18404,12 @@
         </is>
       </c>
       <c r="D260" s="4">
+        <v>163</v>
+      </c>
+      <c r="E260" s="4">
         <v>6</v>
       </c>
-      <c r="E260" s="6" t="inlineStr">
+      <c r="F260" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17740,9 +18523,12 @@
         </is>
       </c>
       <c r="D261" s="4">
+        <v>163</v>
+      </c>
+      <c r="E261" s="4">
         <v>7</v>
       </c>
-      <c r="E261" s="6" t="inlineStr">
+      <c r="F261" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17863,9 +18649,12 @@
         </is>
       </c>
       <c r="D262" s="4">
+        <v>163</v>
+      </c>
+      <c r="E262" s="4">
         <v>8</v>
       </c>
-      <c r="E262" s="6" t="inlineStr">
+      <c r="F262" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17986,9 +18775,12 @@
         </is>
       </c>
       <c r="D263" s="4">
+        <v>163</v>
+      </c>
+      <c r="E263" s="4">
         <v>9</v>
       </c>
-      <c r="E263" s="6" t="inlineStr">
+      <c r="F263" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18154,9 +18946,12 @@
         </is>
       </c>
       <c r="D264" s="4">
+        <v>163</v>
+      </c>
+      <c r="E264" s="4">
         <v>10</v>
       </c>
-      <c r="E264" s="6" t="inlineStr">
+      <c r="F264" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18300,9 +19095,12 @@
         </is>
       </c>
       <c r="D265" s="4">
+        <v>163</v>
+      </c>
+      <c r="E265" s="4">
         <v>11</v>
       </c>
-      <c r="E265" s="6" t="inlineStr">
+      <c r="F265" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18461,9 +19259,12 @@
         </is>
       </c>
       <c r="D266" s="4">
+        <v>163</v>
+      </c>
+      <c r="E266" s="4">
         <v>12</v>
       </c>
-      <c r="E266" s="6" t="inlineStr">
+      <c r="F266" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18629,9 +19430,12 @@
         </is>
       </c>
       <c r="D267" s="4">
+        <v>163</v>
+      </c>
+      <c r="E267" s="4">
         <v>13</v>
       </c>
-      <c r="E267" s="6" t="inlineStr">
+      <c r="F267" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18812,9 +19616,12 @@
         </is>
       </c>
       <c r="D268" s="4">
+        <v>163</v>
+      </c>
+      <c r="E268" s="4">
         <v>14</v>
       </c>
-      <c r="E268" s="6" t="inlineStr">
+      <c r="F268" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18950,9 +19757,12 @@
         </is>
       </c>
       <c r="D269" s="4">
+        <v>163</v>
+      </c>
+      <c r="E269" s="4">
         <v>15</v>
       </c>
-      <c r="E269" s="6" t="inlineStr">
+      <c r="F269" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19066,9 +19876,12 @@
         </is>
       </c>
       <c r="D270" s="4">
+        <v>163</v>
+      </c>
+      <c r="E270" s="4">
         <v>16</v>
       </c>
-      <c r="E270" s="6" t="inlineStr">
+      <c r="F270" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19182,9 +19995,12 @@
         </is>
       </c>
       <c r="D271" s="4">
+        <v>163</v>
+      </c>
+      <c r="E271" s="4">
         <v>17</v>
       </c>
-      <c r="E271" s="6" t="inlineStr">
+      <c r="F271" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19290,9 +20106,12 @@
         </is>
       </c>
       <c r="D272" s="4">
+        <v>163</v>
+      </c>
+      <c r="E272" s="4">
         <v>18</v>
       </c>
-      <c r="E272" s="6" t="inlineStr">
+      <c r="F272" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19391,9 +20210,12 @@
         </is>
       </c>
       <c r="D273" s="4">
+        <v>163</v>
+      </c>
+      <c r="E273" s="4">
         <v>19</v>
       </c>
-      <c r="E273" s="6" t="inlineStr">
+      <c r="F273" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19529,9 +20351,12 @@
         </is>
       </c>
       <c r="D274" s="4">
+        <v>163</v>
+      </c>
+      <c r="E274" s="4">
         <v>20</v>
       </c>
-      <c r="E274" s="6" t="inlineStr">
+      <c r="F274" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19677,7 +20502,10 @@
       <c r="D275" s="4">
         <v>1</v>
       </c>
-      <c r="E275" s="6" t="inlineStr">
+      <c r="E275" s="4">
+        <v>1</v>
+      </c>
+      <c r="F275" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19738,9 +20566,12 @@
         </is>
       </c>
       <c r="D276" s="4">
+        <v>5</v>
+      </c>
+      <c r="E276" s="4">
         <v>1</v>
       </c>
-      <c r="E276" s="6" t="inlineStr">
+      <c r="F276" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19801,9 +20632,12 @@
         </is>
       </c>
       <c r="D277" s="4">
+        <v>5</v>
+      </c>
+      <c r="E277" s="4">
         <v>2</v>
       </c>
-      <c r="E277" s="6" t="inlineStr">
+      <c r="F277" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19864,9 +20698,12 @@
         </is>
       </c>
       <c r="D278" s="4">
+        <v>5</v>
+      </c>
+      <c r="E278" s="4">
         <v>3</v>
       </c>
-      <c r="E278" s="6" t="inlineStr">
+      <c r="F278" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19927,9 +20764,12 @@
         </is>
       </c>
       <c r="D279" s="4">
+        <v>5</v>
+      </c>
+      <c r="E279" s="4">
         <v>4</v>
       </c>
-      <c r="E279" s="6" t="inlineStr">
+      <c r="F279" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19992,7 +20832,10 @@
       <c r="D280" s="4">
         <v>5</v>
       </c>
-      <c r="E280" s="6" t="inlineStr">
+      <c r="E280" s="4">
+        <v>5</v>
+      </c>
+      <c r="F280" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20055,7 +20898,10 @@
       <c r="D281" s="4">
         <v>1</v>
       </c>
-      <c r="E281" s="6" t="inlineStr">
+      <c r="E281" s="4">
+        <v>1</v>
+      </c>
+      <c r="F281" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20126,7 +20972,10 @@
       <c r="D282" s="4">
         <v>1</v>
       </c>
-      <c r="E282" s="6" t="inlineStr">
+      <c r="E282" s="4">
+        <v>1</v>
+      </c>
+      <c r="F282" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20249,7 +21098,10 @@
       <c r="D283" s="4">
         <v>1</v>
       </c>
-      <c r="E283" s="6" t="inlineStr">
+      <c r="E283" s="4">
+        <v>1</v>
+      </c>
+      <c r="F283" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20319,9 +21171,12 @@
         </is>
       </c>
       <c r="D284" s="4">
+        <v>2</v>
+      </c>
+      <c r="E284" s="4">
         <v>1</v>
       </c>
-      <c r="E284" s="6" t="inlineStr">
+      <c r="F284" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20407,7 +21262,10 @@
       <c r="D285" s="4">
         <v>2</v>
       </c>
-      <c r="E285" s="6" t="inlineStr">
+      <c r="E285" s="4">
+        <v>2</v>
+      </c>
+      <c r="F285" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20485,7 +21343,10 @@
       <c r="D286" s="4">
         <v>1</v>
       </c>
-      <c r="E286" s="6" t="inlineStr">
+      <c r="E286" s="4">
+        <v>1</v>
+      </c>
+      <c r="F286" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20546,9 +21407,12 @@
         </is>
       </c>
       <c r="D287" s="4">
+        <v>2</v>
+      </c>
+      <c r="E287" s="4">
         <v>1</v>
       </c>
-      <c r="E287" s="6" t="inlineStr">
+      <c r="F287" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20619,7 +21483,10 @@
       <c r="D288" s="4">
         <v>2</v>
       </c>
-      <c r="E288" s="6" t="inlineStr">
+      <c r="E288" s="4">
+        <v>2</v>
+      </c>
+      <c r="F288" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20690,7 +21557,10 @@
       <c r="D289" s="4">
         <v>1</v>
       </c>
-      <c r="E289" s="6" t="inlineStr">
+      <c r="E289" s="4">
+        <v>1</v>
+      </c>
+      <c r="F289" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20766,9 +21636,12 @@
         </is>
       </c>
       <c r="D290" s="4">
+        <v>2</v>
+      </c>
+      <c r="E290" s="4">
         <v>1</v>
       </c>
-      <c r="E290" s="6" t="inlineStr">
+      <c r="F290" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20854,7 +21727,10 @@
       <c r="D291" s="4">
         <v>2</v>
       </c>
-      <c r="E291" s="6" t="inlineStr">
+      <c r="E291" s="4">
+        <v>2</v>
+      </c>
+      <c r="F291" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20970,7 +21846,10 @@
       <c r="D292" s="4">
         <v>1</v>
       </c>
-      <c r="E292" s="6" t="inlineStr">
+      <c r="E292" s="4">
+        <v>1</v>
+      </c>
+      <c r="F292" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21033,7 +21912,10 @@
       <c r="D293" s="4">
         <v>1</v>
       </c>
-      <c r="E293" s="6" t="inlineStr">
+      <c r="E293" s="4">
+        <v>1</v>
+      </c>
+      <c r="F293" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21162,9 +22044,12 @@
         </is>
       </c>
       <c r="D294" s="4">
+        <v>5</v>
+      </c>
+      <c r="E294" s="4">
         <v>1</v>
       </c>
-      <c r="E294" s="6" t="inlineStr">
+      <c r="F294" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21248,9 +22133,12 @@
         </is>
       </c>
       <c r="D295" s="4">
+        <v>5</v>
+      </c>
+      <c r="E295" s="4">
         <v>2</v>
       </c>
-      <c r="E295" s="6" t="inlineStr">
+      <c r="F295" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21311,9 +22199,12 @@
         </is>
       </c>
       <c r="D296" s="4">
+        <v>5</v>
+      </c>
+      <c r="E296" s="4">
         <v>3</v>
       </c>
-      <c r="E296" s="6" t="inlineStr">
+      <c r="F296" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21374,9 +22265,12 @@
         </is>
       </c>
       <c r="D297" s="4">
+        <v>5</v>
+      </c>
+      <c r="E297" s="4">
         <v>4</v>
       </c>
-      <c r="E297" s="6" t="inlineStr">
+      <c r="F297" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21454,7 +22348,10 @@
       <c r="D298" s="4">
         <v>1</v>
       </c>
-      <c r="E298" s="6" t="inlineStr">
+      <c r="E298" s="4">
+        <v>1</v>
+      </c>
+      <c r="F298" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21524,9 +22421,12 @@
         </is>
       </c>
       <c r="D299" s="4">
+        <v>12</v>
+      </c>
+      <c r="E299" s="4">
         <v>1</v>
       </c>
-      <c r="E299" s="6" t="inlineStr">
+      <c r="F299" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21625,9 +22525,12 @@
         </is>
       </c>
       <c r="D300" s="4">
+        <v>12</v>
+      </c>
+      <c r="E300" s="4">
         <v>2</v>
       </c>
-      <c r="E300" s="6" t="inlineStr">
+      <c r="F300" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21696,9 +22599,12 @@
         </is>
       </c>
       <c r="D301" s="4">
+        <v>12</v>
+      </c>
+      <c r="E301" s="4">
         <v>3</v>
       </c>
-      <c r="E301" s="6" t="inlineStr">
+      <c r="F301" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21759,9 +22665,12 @@
         </is>
       </c>
       <c r="D302" s="4">
+        <v>12</v>
+      </c>
+      <c r="E302" s="4">
         <v>4</v>
       </c>
-      <c r="E302" s="6" t="inlineStr">
+      <c r="F302" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21830,9 +22739,12 @@
         </is>
       </c>
       <c r="D303" s="4">
+        <v>12</v>
+      </c>
+      <c r="E303" s="4">
         <v>5</v>
       </c>
-      <c r="E303" s="6" t="inlineStr">
+      <c r="F303" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21893,9 +22805,12 @@
         </is>
       </c>
       <c r="D304" s="4">
+        <v>12</v>
+      </c>
+      <c r="E304" s="4">
         <v>6</v>
       </c>
-      <c r="E304" s="6" t="inlineStr">
+      <c r="F304" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21956,9 +22871,12 @@
         </is>
       </c>
       <c r="D305" s="4">
+        <v>12</v>
+      </c>
+      <c r="E305" s="4">
         <v>7</v>
       </c>
-      <c r="E305" s="6" t="inlineStr">
+      <c r="F305" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22019,9 +22937,12 @@
         </is>
       </c>
       <c r="D306" s="4">
+        <v>12</v>
+      </c>
+      <c r="E306" s="4">
         <v>8</v>
       </c>
-      <c r="E306" s="6" t="inlineStr">
+      <c r="F306" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22082,9 +23003,12 @@
         </is>
       </c>
       <c r="D307" s="4">
+        <v>12</v>
+      </c>
+      <c r="E307" s="4">
         <v>9</v>
       </c>
-      <c r="E307" s="6" t="inlineStr">
+      <c r="F307" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22153,9 +23077,12 @@
         </is>
       </c>
       <c r="D308" s="4">
+        <v>12</v>
+      </c>
+      <c r="E308" s="4">
         <v>10</v>
       </c>
-      <c r="E308" s="6" t="inlineStr">
+      <c r="F308" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22216,9 +23143,12 @@
         </is>
       </c>
       <c r="D309" s="4">
+        <v>12</v>
+      </c>
+      <c r="E309" s="4">
         <v>11</v>
       </c>
-      <c r="E309" s="6" t="inlineStr">
+      <c r="F309" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22290,7 +23220,10 @@
       <c r="D310" s="4">
         <v>12</v>
       </c>
-      <c r="E310" s="6" t="inlineStr">
+      <c r="E310" s="4">
+        <v>12</v>
+      </c>
+      <c r="F310" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22351,9 +23284,12 @@
         </is>
       </c>
       <c r="D311" s="4">
+        <v>7</v>
+      </c>
+      <c r="E311" s="4">
         <v>1</v>
       </c>
-      <c r="E311" s="6" t="inlineStr">
+      <c r="F311" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22414,9 +23350,12 @@
         </is>
       </c>
       <c r="D312" s="4">
+        <v>7</v>
+      </c>
+      <c r="E312" s="4">
         <v>2</v>
       </c>
-      <c r="E312" s="6" t="inlineStr">
+      <c r="F312" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22477,9 +23416,12 @@
         </is>
       </c>
       <c r="D313" s="4">
+        <v>7</v>
+      </c>
+      <c r="E313" s="4">
         <v>3</v>
       </c>
-      <c r="E313" s="6" t="inlineStr">
+      <c r="F313" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22540,9 +23482,12 @@
         </is>
       </c>
       <c r="D314" s="4">
+        <v>7</v>
+      </c>
+      <c r="E314" s="4">
         <v>4</v>
       </c>
-      <c r="E314" s="6" t="inlineStr">
+      <c r="F314" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22603,9 +23548,12 @@
         </is>
       </c>
       <c r="D315" s="4">
+        <v>7</v>
+      </c>
+      <c r="E315" s="4">
         <v>5</v>
       </c>
-      <c r="E315" s="6" t="inlineStr">
+      <c r="F315" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22666,9 +23614,12 @@
         </is>
       </c>
       <c r="D316" s="4">
+        <v>7</v>
+      </c>
+      <c r="E316" s="4">
         <v>6</v>
       </c>
-      <c r="E316" s="6" t="inlineStr">
+      <c r="F316" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22731,7 +23682,10 @@
       <c r="D317" s="4">
         <v>7</v>
       </c>
-      <c r="E317" s="6" t="inlineStr">
+      <c r="E317" s="4">
+        <v>7</v>
+      </c>
+      <c r="F317" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22792,9 +23746,12 @@
         </is>
       </c>
       <c r="D318" s="4">
+        <v>7</v>
+      </c>
+      <c r="E318" s="4">
         <v>1</v>
       </c>
-      <c r="E318" s="6" t="inlineStr">
+      <c r="F318" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22864,9 +23821,12 @@
         </is>
       </c>
       <c r="D319" s="4">
+        <v>7</v>
+      </c>
+      <c r="E319" s="4">
         <v>2</v>
       </c>
-      <c r="E319" s="6" t="inlineStr">
+      <c r="F319" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22936,9 +23896,12 @@
         </is>
       </c>
       <c r="D320" s="4">
+        <v>7</v>
+      </c>
+      <c r="E320" s="4">
         <v>3</v>
       </c>
-      <c r="E320" s="6" t="inlineStr">
+      <c r="F320" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23008,9 +23971,12 @@
         </is>
       </c>
       <c r="D321" s="4">
+        <v>7</v>
+      </c>
+      <c r="E321" s="4">
         <v>4</v>
       </c>
-      <c r="E321" s="6" t="inlineStr">
+      <c r="F321" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23080,9 +24046,12 @@
         </is>
       </c>
       <c r="D322" s="4">
+        <v>7</v>
+      </c>
+      <c r="E322" s="4">
         <v>5</v>
       </c>
-      <c r="E322" s="6" t="inlineStr">
+      <c r="F322" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23152,9 +24121,12 @@
         </is>
       </c>
       <c r="D323" s="4">
+        <v>7</v>
+      </c>
+      <c r="E323" s="4">
         <v>6</v>
       </c>
-      <c r="E323" s="6" t="inlineStr">
+      <c r="F323" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23226,7 +24198,10 @@
       <c r="D324" s="4">
         <v>7</v>
       </c>
-      <c r="E324" s="6" t="inlineStr">
+      <c r="E324" s="4">
+        <v>7</v>
+      </c>
+      <c r="F324" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23296,9 +24271,12 @@
         </is>
       </c>
       <c r="D325" s="4">
+        <v>35</v>
+      </c>
+      <c r="E325" s="4">
         <v>1</v>
       </c>
-      <c r="E325" s="6" t="inlineStr">
+      <c r="F325" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23368,9 +24346,12 @@
         </is>
       </c>
       <c r="D326" s="4">
+        <v>35</v>
+      </c>
+      <c r="E326" s="4">
         <v>2</v>
       </c>
-      <c r="E326" s="6" t="inlineStr">
+      <c r="F326" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23440,9 +24421,12 @@
         </is>
       </c>
       <c r="D327" s="4">
+        <v>35</v>
+      </c>
+      <c r="E327" s="4">
         <v>3</v>
       </c>
-      <c r="E327" s="6" t="inlineStr">
+      <c r="F327" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23512,9 +24496,12 @@
         </is>
       </c>
       <c r="D328" s="4">
+        <v>35</v>
+      </c>
+      <c r="E328" s="4">
         <v>4</v>
       </c>
-      <c r="E328" s="6" t="inlineStr">
+      <c r="F328" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23575,9 +24562,12 @@
         </is>
       </c>
       <c r="D329" s="4">
+        <v>35</v>
+      </c>
+      <c r="E329" s="4">
         <v>5</v>
       </c>
-      <c r="E329" s="6" t="inlineStr">
+      <c r="F329" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23647,9 +24637,12 @@
         </is>
       </c>
       <c r="D330" s="4">
+        <v>35</v>
+      </c>
+      <c r="E330" s="4">
         <v>6</v>
       </c>
-      <c r="E330" s="6" t="inlineStr">
+      <c r="F330" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23719,9 +24712,12 @@
         </is>
       </c>
       <c r="D331" s="4">
+        <v>35</v>
+      </c>
+      <c r="E331" s="4">
         <v>7</v>
       </c>
-      <c r="E331" s="6" t="inlineStr">
+      <c r="F331" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23791,9 +24787,12 @@
         </is>
       </c>
       <c r="D332" s="4">
+        <v>35</v>
+      </c>
+      <c r="E332" s="4">
         <v>8</v>
       </c>
-      <c r="E332" s="6" t="inlineStr">
+      <c r="F332" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23863,9 +24862,12 @@
         </is>
       </c>
       <c r="D333" s="4">
+        <v>35</v>
+      </c>
+      <c r="E333" s="4">
         <v>9</v>
       </c>
-      <c r="E333" s="6" t="inlineStr">
+      <c r="F333" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23935,9 +24937,12 @@
         </is>
       </c>
       <c r="D334" s="4">
+        <v>35</v>
+      </c>
+      <c r="E334" s="4">
         <v>10</v>
       </c>
-      <c r="E334" s="6" t="inlineStr">
+      <c r="F334" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24007,9 +25012,12 @@
         </is>
       </c>
       <c r="D335" s="4">
+        <v>35</v>
+      </c>
+      <c r="E335" s="4">
         <v>11</v>
       </c>
-      <c r="E335" s="6" t="inlineStr">
+      <c r="F335" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24079,9 +25087,12 @@
         </is>
       </c>
       <c r="D336" s="4">
+        <v>35</v>
+      </c>
+      <c r="E336" s="4">
         <v>12</v>
       </c>
-      <c r="E336" s="6" t="inlineStr">
+      <c r="F336" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24151,9 +25162,12 @@
         </is>
       </c>
       <c r="D337" s="4">
+        <v>35</v>
+      </c>
+      <c r="E337" s="4">
         <v>13</v>
       </c>
-      <c r="E337" s="6" t="inlineStr">
+      <c r="F337" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24223,9 +25237,12 @@
         </is>
       </c>
       <c r="D338" s="4">
+        <v>35</v>
+      </c>
+      <c r="E338" s="4">
         <v>14</v>
       </c>
-      <c r="E338" s="6" t="inlineStr">
+      <c r="F338" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24295,9 +25312,12 @@
         </is>
       </c>
       <c r="D339" s="4">
+        <v>35</v>
+      </c>
+      <c r="E339" s="4">
         <v>15</v>
       </c>
-      <c r="E339" s="6" t="inlineStr">
+      <c r="F339" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24367,9 +25387,12 @@
         </is>
       </c>
       <c r="D340" s="4">
+        <v>35</v>
+      </c>
+      <c r="E340" s="4">
         <v>16</v>
       </c>
-      <c r="E340" s="6" t="inlineStr">
+      <c r="F340" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24439,9 +25462,12 @@
         </is>
       </c>
       <c r="D341" s="4">
+        <v>35</v>
+      </c>
+      <c r="E341" s="4">
         <v>17</v>
       </c>
-      <c r="E341" s="6" t="inlineStr">
+      <c r="F341" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24511,9 +25537,12 @@
         </is>
       </c>
       <c r="D342" s="4">
+        <v>35</v>
+      </c>
+      <c r="E342" s="4">
         <v>18</v>
       </c>
-      <c r="E342" s="6" t="inlineStr">
+      <c r="F342" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24583,9 +25612,12 @@
         </is>
       </c>
       <c r="D343" s="4">
+        <v>35</v>
+      </c>
+      <c r="E343" s="4">
         <v>19</v>
       </c>
-      <c r="E343" s="6" t="inlineStr">
+      <c r="F343" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24655,9 +25687,12 @@
         </is>
       </c>
       <c r="D344" s="4">
+        <v>35</v>
+      </c>
+      <c r="E344" s="4">
         <v>20</v>
       </c>
-      <c r="E344" s="6" t="inlineStr">
+      <c r="F344" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24727,9 +25762,12 @@
         </is>
       </c>
       <c r="D345" s="4">
+        <v>6</v>
+      </c>
+      <c r="E345" s="4">
         <v>1</v>
       </c>
-      <c r="E345" s="6" t="inlineStr">
+      <c r="F345" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24783,9 +25821,12 @@
         </is>
       </c>
       <c r="D346" s="4">
+        <v>6</v>
+      </c>
+      <c r="E346" s="4">
         <v>2</v>
       </c>
-      <c r="E346" s="6" t="inlineStr">
+      <c r="F346" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24839,9 +25880,12 @@
         </is>
       </c>
       <c r="D347" s="4">
+        <v>6</v>
+      </c>
+      <c r="E347" s="4">
         <v>3</v>
       </c>
-      <c r="E347" s="6" t="inlineStr">
+      <c r="F347" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24895,9 +25939,12 @@
         </is>
       </c>
       <c r="D348" s="4">
+        <v>6</v>
+      </c>
+      <c r="E348" s="4">
         <v>4</v>
       </c>
-      <c r="E348" s="6" t="inlineStr">
+      <c r="F348" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24951,9 +25998,12 @@
         </is>
       </c>
       <c r="D349" s="4">
+        <v>6</v>
+      </c>
+      <c r="E349" s="4">
         <v>5</v>
       </c>
-      <c r="E349" s="6" t="inlineStr">
+      <c r="F349" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25009,7 +26059,10 @@
       <c r="D350" s="4">
         <v>6</v>
       </c>
-      <c r="E350" s="6" t="inlineStr">
+      <c r="E350" s="4">
+        <v>6</v>
+      </c>
+      <c r="F350" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25065,7 +26118,10 @@
       <c r="D351" s="4">
         <v>1</v>
       </c>
-      <c r="E351" s="6" t="inlineStr">
+      <c r="E351" s="4">
+        <v>1</v>
+      </c>
+      <c r="F351" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25119,9 +26175,12 @@
         </is>
       </c>
       <c r="D352" s="4">
+        <v>2</v>
+      </c>
+      <c r="E352" s="4">
         <v>1</v>
       </c>
-      <c r="E352" s="6" t="inlineStr">
+      <c r="F352" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25177,7 +26236,10 @@
       <c r="D353" s="4">
         <v>2</v>
       </c>
-      <c r="E353" s="6" t="inlineStr">
+      <c r="E353" s="4">
+        <v>2</v>
+      </c>
+      <c r="F353" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25233,7 +26295,10 @@
       <c r="D354" s="4">
         <v>1</v>
       </c>
-      <c r="E354" s="6" t="inlineStr">
+      <c r="E354" s="4">
+        <v>1</v>
+      </c>
+      <c r="F354" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25287,9 +26352,12 @@
         </is>
       </c>
       <c r="D355" s="4">
+        <v>28</v>
+      </c>
+      <c r="E355" s="4">
         <v>1</v>
       </c>
-      <c r="E355" s="6" t="inlineStr">
+      <c r="F355" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25343,9 +26411,12 @@
         </is>
       </c>
       <c r="D356" s="4">
+        <v>28</v>
+      </c>
+      <c r="E356" s="4">
         <v>2</v>
       </c>
-      <c r="E356" s="6" t="inlineStr">
+      <c r="F356" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25399,9 +26470,12 @@
         </is>
       </c>
       <c r="D357" s="4">
+        <v>28</v>
+      </c>
+      <c r="E357" s="4">
         <v>3</v>
       </c>
-      <c r="E357" s="6" t="inlineStr">
+      <c r="F357" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25455,9 +26529,12 @@
         </is>
       </c>
       <c r="D358" s="4">
+        <v>28</v>
+      </c>
+      <c r="E358" s="4">
         <v>4</v>
       </c>
-      <c r="E358" s="6" t="inlineStr">
+      <c r="F358" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25511,9 +26588,12 @@
         </is>
       </c>
       <c r="D359" s="4">
+        <v>28</v>
+      </c>
+      <c r="E359" s="4">
         <v>5</v>
       </c>
-      <c r="E359" s="6" t="inlineStr">
+      <c r="F359" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25567,9 +26647,12 @@
         </is>
       </c>
       <c r="D360" s="4">
+        <v>28</v>
+      </c>
+      <c r="E360" s="4">
         <v>6</v>
       </c>
-      <c r="E360" s="6" t="inlineStr">
+      <c r="F360" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25623,9 +26706,12 @@
         </is>
       </c>
       <c r="D361" s="4">
+        <v>28</v>
+      </c>
+      <c r="E361" s="4">
         <v>7</v>
       </c>
-      <c r="E361" s="6" t="inlineStr">
+      <c r="F361" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25679,9 +26765,12 @@
         </is>
       </c>
       <c r="D362" s="4">
+        <v>28</v>
+      </c>
+      <c r="E362" s="4">
         <v>8</v>
       </c>
-      <c r="E362" s="6" t="inlineStr">
+      <c r="F362" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25735,9 +26824,12 @@
         </is>
       </c>
       <c r="D363" s="4">
+        <v>28</v>
+      </c>
+      <c r="E363" s="4">
         <v>9</v>
       </c>
-      <c r="E363" s="6" t="inlineStr">
+      <c r="F363" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25791,9 +26883,12 @@
         </is>
       </c>
       <c r="D364" s="4">
+        <v>28</v>
+      </c>
+      <c r="E364" s="4">
         <v>10</v>
       </c>
-      <c r="E364" s="6" t="inlineStr">
+      <c r="F364" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25847,9 +26942,12 @@
         </is>
       </c>
       <c r="D365" s="4">
+        <v>28</v>
+      </c>
+      <c r="E365" s="4">
         <v>11</v>
       </c>
-      <c r="E365" s="6" t="inlineStr">
+      <c r="F365" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25903,9 +27001,12 @@
         </is>
       </c>
       <c r="D366" s="4">
+        <v>28</v>
+      </c>
+      <c r="E366" s="4">
         <v>12</v>
       </c>
-      <c r="E366" s="6" t="inlineStr">
+      <c r="F366" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25959,9 +27060,12 @@
         </is>
       </c>
       <c r="D367" s="4">
+        <v>28</v>
+      </c>
+      <c r="E367" s="4">
         <v>13</v>
       </c>
-      <c r="E367" s="6" t="inlineStr">
+      <c r="F367" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26015,9 +27119,12 @@
         </is>
       </c>
       <c r="D368" s="4">
+        <v>28</v>
+      </c>
+      <c r="E368" s="4">
         <v>14</v>
       </c>
-      <c r="E368" s="6" t="inlineStr">
+      <c r="F368" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26071,9 +27178,12 @@
         </is>
       </c>
       <c r="D369" s="4">
+        <v>28</v>
+      </c>
+      <c r="E369" s="4">
         <v>15</v>
       </c>
-      <c r="E369" s="6" t="inlineStr">
+      <c r="F369" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26127,9 +27237,12 @@
         </is>
       </c>
       <c r="D370" s="4">
+        <v>28</v>
+      </c>
+      <c r="E370" s="4">
         <v>16</v>
       </c>
-      <c r="E370" s="6" t="inlineStr">
+      <c r="F370" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26183,9 +27296,12 @@
         </is>
       </c>
       <c r="D371" s="4">
+        <v>28</v>
+      </c>
+      <c r="E371" s="4">
         <v>17</v>
       </c>
-      <c r="E371" s="6" t="inlineStr">
+      <c r="F371" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26239,9 +27355,12 @@
         </is>
       </c>
       <c r="D372" s="4">
+        <v>28</v>
+      </c>
+      <c r="E372" s="4">
         <v>18</v>
       </c>
-      <c r="E372" s="6" t="inlineStr">
+      <c r="F372" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26295,9 +27414,12 @@
         </is>
       </c>
       <c r="D373" s="4">
+        <v>28</v>
+      </c>
+      <c r="E373" s="4">
         <v>19</v>
       </c>
-      <c r="E373" s="6" t="inlineStr">
+      <c r="F373" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26351,9 +27473,12 @@
         </is>
       </c>
       <c r="D374" s="4">
+        <v>28</v>
+      </c>
+      <c r="E374" s="4">
         <v>20</v>
       </c>
-      <c r="E374" s="6" t="inlineStr">
+      <c r="F374" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26409,7 +27534,10 @@
       <c r="D375" s="4">
         <v>1</v>
       </c>
-      <c r="E375" s="6" t="inlineStr">
+      <c r="E375" s="4">
+        <v>1</v>
+      </c>
+      <c r="F375" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26481,7 +27609,10 @@
       <c r="D376" s="4">
         <v>1</v>
       </c>
-      <c r="E376" s="6" t="inlineStr">
+      <c r="E376" s="4">
+        <v>1</v>
+      </c>
+      <c r="F376" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26544,7 +27675,10 @@
       <c r="D377" s="4">
         <v>1</v>
       </c>
-      <c r="E377" s="6" t="inlineStr">
+      <c r="E377" s="4">
+        <v>1</v>
+      </c>
+      <c r="F377" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26605,9 +27739,12 @@
         </is>
       </c>
       <c r="D378" s="4">
+        <v>4</v>
+      </c>
+      <c r="E378" s="4">
         <v>1</v>
       </c>
-      <c r="E378" s="6" t="inlineStr">
+      <c r="F378" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26676,9 +27813,12 @@
         </is>
       </c>
       <c r="D379" s="4">
+        <v>4</v>
+      </c>
+      <c r="E379" s="4">
         <v>2</v>
       </c>
-      <c r="E379" s="6" t="inlineStr">
+      <c r="F379" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26762,9 +27902,12 @@
         </is>
       </c>
       <c r="D380" s="4">
+        <v>4</v>
+      </c>
+      <c r="E380" s="4">
         <v>3</v>
       </c>
-      <c r="E380" s="6" t="inlineStr">
+      <c r="F380" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26850,7 +27993,10 @@
       <c r="D381" s="4">
         <v>4</v>
       </c>
-      <c r="E381" s="6" t="inlineStr">
+      <c r="E381" s="4">
+        <v>4</v>
+      </c>
+      <c r="F381" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26956,9 +28102,12 @@
         </is>
       </c>
       <c r="D382" s="4">
+        <v>2</v>
+      </c>
+      <c r="E382" s="4">
         <v>1</v>
       </c>
-      <c r="E382" s="6" t="inlineStr">
+      <c r="F382" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27021,7 +28170,10 @@
       <c r="D383" s="4">
         <v>2</v>
       </c>
-      <c r="E383" s="6" t="inlineStr">
+      <c r="E383" s="4">
+        <v>2</v>
+      </c>
+      <c r="F383" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27084,7 +28236,10 @@
       <c r="D384" s="4">
         <v>1</v>
       </c>
-      <c r="E384" s="6" t="inlineStr">
+      <c r="E384" s="4">
+        <v>1</v>
+      </c>
+      <c r="F384" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27153,9 +28308,12 @@
         </is>
       </c>
       <c r="D385" s="4">
+        <v>4</v>
+      </c>
+      <c r="E385" s="4">
         <v>1</v>
       </c>
-      <c r="E385" s="6" t="inlineStr">
+      <c r="F385" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27231,9 +28389,12 @@
         </is>
       </c>
       <c r="D386" s="4">
+        <v>4</v>
+      </c>
+      <c r="E386" s="4">
         <v>2</v>
       </c>
-      <c r="E386" s="6" t="inlineStr">
+      <c r="F386" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27309,9 +28470,12 @@
         </is>
       </c>
       <c r="D387" s="4">
+        <v>4</v>
+      </c>
+      <c r="E387" s="4">
         <v>3</v>
       </c>
-      <c r="E387" s="6" t="inlineStr">
+      <c r="F387" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27389,7 +28553,10 @@
       <c r="D388" s="4">
         <v>4</v>
       </c>
-      <c r="E388" s="6" t="inlineStr">
+      <c r="E388" s="4">
+        <v>4</v>
+      </c>
+      <c r="F388" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27467,7 +28634,10 @@
       <c r="D389" s="4">
         <v>1</v>
       </c>
-      <c r="E389" s="6" t="inlineStr">
+      <c r="E389" s="4">
+        <v>1</v>
+      </c>
+      <c r="F389" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27551,9 +28721,12 @@
         </is>
       </c>
       <c r="D390" s="4">
+        <v>16</v>
+      </c>
+      <c r="E390" s="4">
         <v>1</v>
       </c>
-      <c r="E390" s="6" t="inlineStr">
+      <c r="F390" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27659,9 +28832,12 @@
         </is>
       </c>
       <c r="D391" s="4">
+        <v>16</v>
+      </c>
+      <c r="E391" s="4">
         <v>2</v>
       </c>
-      <c r="E391" s="6" t="inlineStr">
+      <c r="F391" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27782,9 +28958,12 @@
         </is>
       </c>
       <c r="D392" s="4">
+        <v>16</v>
+      </c>
+      <c r="E392" s="4">
         <v>3</v>
       </c>
-      <c r="E392" s="6" t="inlineStr">
+      <c r="F392" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27980,9 +29159,12 @@
         </is>
       </c>
       <c r="D393" s="4">
+        <v>16</v>
+      </c>
+      <c r="E393" s="4">
         <v>4</v>
       </c>
-      <c r="E393" s="6" t="inlineStr">
+      <c r="F393" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28163,9 +29345,12 @@
         </is>
       </c>
       <c r="D394" s="4">
+        <v>16</v>
+      </c>
+      <c r="E394" s="4">
         <v>5</v>
       </c>
-      <c r="E394" s="6" t="inlineStr">
+      <c r="F394" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28279,9 +29464,12 @@
         </is>
       </c>
       <c r="D395" s="4">
+        <v>16</v>
+      </c>
+      <c r="E395" s="4">
         <v>6</v>
       </c>
-      <c r="E395" s="6" t="inlineStr">
+      <c r="F395" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28372,9 +29560,12 @@
         </is>
       </c>
       <c r="D396" s="4">
+        <v>16</v>
+      </c>
+      <c r="E396" s="4">
         <v>7</v>
       </c>
-      <c r="E396" s="6" t="inlineStr">
+      <c r="F396" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28563,9 +29754,12 @@
         </is>
       </c>
       <c r="D397" s="4">
+        <v>16</v>
+      </c>
+      <c r="E397" s="4">
         <v>8</v>
       </c>
-      <c r="E397" s="6" t="inlineStr">
+      <c r="F397" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28724,9 +29918,12 @@
         </is>
       </c>
       <c r="D398" s="4">
+        <v>16</v>
+      </c>
+      <c r="E398" s="4">
         <v>9</v>
       </c>
-      <c r="E398" s="6" t="inlineStr">
+      <c r="F398" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28877,9 +30074,12 @@
         </is>
       </c>
       <c r="D399" s="4">
+        <v>16</v>
+      </c>
+      <c r="E399" s="4">
         <v>10</v>
       </c>
-      <c r="E399" s="6" t="inlineStr">
+      <c r="F399" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29015,9 +30215,12 @@
         </is>
       </c>
       <c r="D400" s="4">
+        <v>16</v>
+      </c>
+      <c r="E400" s="4">
         <v>11</v>
       </c>
-      <c r="E400" s="6" t="inlineStr">
+      <c r="F400" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29206,9 +30409,12 @@
         </is>
       </c>
       <c r="D401" s="4">
+        <v>16</v>
+      </c>
+      <c r="E401" s="4">
         <v>12</v>
       </c>
-      <c r="E401" s="6" t="inlineStr">
+      <c r="F401" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29404,9 +30610,12 @@
         </is>
       </c>
       <c r="D402" s="4">
+        <v>16</v>
+      </c>
+      <c r="E402" s="4">
         <v>13</v>
       </c>
-      <c r="E402" s="6" t="inlineStr">
+      <c r="F402" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29557,9 +30766,12 @@
         </is>
       </c>
       <c r="D403" s="4">
+        <v>16</v>
+      </c>
+      <c r="E403" s="4">
         <v>14</v>
       </c>
-      <c r="E403" s="6" t="inlineStr">
+      <c r="F403" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29695,9 +30907,12 @@
         </is>
       </c>
       <c r="D404" s="4">
+        <v>16</v>
+      </c>
+      <c r="E404" s="4">
         <v>15</v>
       </c>
-      <c r="E404" s="6" t="inlineStr">
+      <c r="F404" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29835,7 +31050,10 @@
       <c r="D405" s="4">
         <v>16</v>
       </c>
-      <c r="E405" s="6" t="inlineStr">
+      <c r="E405" s="4">
+        <v>16</v>
+      </c>
+      <c r="F405" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29926,9 +31144,12 @@
         </is>
       </c>
       <c r="D406" s="4">
+        <v>2</v>
+      </c>
+      <c r="E406" s="4">
         <v>1</v>
       </c>
-      <c r="E406" s="6" t="inlineStr">
+      <c r="F406" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29991,7 +31212,10 @@
       <c r="D407" s="4">
         <v>2</v>
       </c>
-      <c r="E407" s="6" t="inlineStr">
+      <c r="E407" s="4">
+        <v>2</v>
+      </c>
+      <c r="F407" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30054,7 +31278,10 @@
       <c r="D408" s="4">
         <v>1</v>
       </c>
-      <c r="E408" s="6" t="inlineStr">
+      <c r="E408" s="4">
+        <v>1</v>
+      </c>
+      <c r="F408" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30138,9 +31365,12 @@
         </is>
       </c>
       <c r="D409" s="4">
+        <v>2</v>
+      </c>
+      <c r="E409" s="4">
         <v>1</v>
       </c>
-      <c r="E409" s="6" t="inlineStr">
+      <c r="F409" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30271,7 +31501,10 @@
       <c r="D410" s="4">
         <v>2</v>
       </c>
-      <c r="E410" s="6" t="inlineStr">
+      <c r="E410" s="4">
+        <v>2</v>
+      </c>
+      <c r="F410" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30362,9 +31595,12 @@
         </is>
       </c>
       <c r="D411" s="4">
+        <v>2</v>
+      </c>
+      <c r="E411" s="4">
         <v>1</v>
       </c>
-      <c r="E411" s="6" t="inlineStr">
+      <c r="F411" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30427,7 +31663,10 @@
       <c r="D412" s="4">
         <v>2</v>
       </c>
-      <c r="E412" s="6" t="inlineStr">
+      <c r="E412" s="4">
+        <v>2</v>
+      </c>
+      <c r="F412" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30490,7 +31729,10 @@
       <c r="D413" s="4">
         <v>1</v>
       </c>
-      <c r="E413" s="6" t="inlineStr">
+      <c r="E413" s="4">
+        <v>1</v>
+      </c>
+      <c r="F413" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30574,9 +31816,12 @@
         </is>
       </c>
       <c r="D414" s="4">
+        <v>3</v>
+      </c>
+      <c r="E414" s="4">
         <v>1</v>
       </c>
-      <c r="E414" s="6" t="inlineStr">
+      <c r="F414" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30667,9 +31912,12 @@
         </is>
       </c>
       <c r="D415" s="4">
+        <v>3</v>
+      </c>
+      <c r="E415" s="4">
         <v>2</v>
       </c>
-      <c r="E415" s="6" t="inlineStr">
+      <c r="F415" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30807,7 +32055,10 @@
       <c r="D416" s="4">
         <v>3</v>
       </c>
-      <c r="E416" s="6" t="inlineStr">
+      <c r="E416" s="4">
+        <v>3</v>
+      </c>
+      <c r="F416" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30938,7 +32189,10 @@
       <c r="D417" s="4">
         <v>1</v>
       </c>
-      <c r="E417" s="6" t="inlineStr">
+      <c r="E417" s="4">
+        <v>1</v>
+      </c>
+      <c r="F417" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31008,9 +32262,12 @@
         </is>
       </c>
       <c r="D418" s="4">
+        <v>5</v>
+      </c>
+      <c r="E418" s="4">
         <v>1</v>
       </c>
-      <c r="E418" s="6" t="inlineStr">
+      <c r="F418" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31071,9 +32328,12 @@
         </is>
       </c>
       <c r="D419" s="4">
+        <v>5</v>
+      </c>
+      <c r="E419" s="4">
         <v>2</v>
       </c>
-      <c r="E419" s="6" t="inlineStr">
+      <c r="F419" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31134,9 +32394,12 @@
         </is>
       </c>
       <c r="D420" s="4">
+        <v>5</v>
+      </c>
+      <c r="E420" s="4">
         <v>3</v>
       </c>
-      <c r="E420" s="6" t="inlineStr">
+      <c r="F420" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31197,9 +32460,12 @@
         </is>
       </c>
       <c r="D421" s="4">
+        <v>5</v>
+      </c>
+      <c r="E421" s="4">
         <v>4</v>
       </c>
-      <c r="E421" s="6" t="inlineStr">
+      <c r="F421" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31262,7 +32528,10 @@
       <c r="D422" s="4">
         <v>5</v>
       </c>
-      <c r="E422" s="6" t="inlineStr">
+      <c r="E422" s="4">
+        <v>5</v>
+      </c>
+      <c r="F422" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31331,9 +32600,12 @@
         </is>
       </c>
       <c r="D423" s="4">
+        <v>16</v>
+      </c>
+      <c r="E423" s="4">
         <v>1</v>
       </c>
-      <c r="E423" s="6" t="inlineStr">
+      <c r="F423" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31394,9 +32666,12 @@
         </is>
       </c>
       <c r="D424" s="4">
+        <v>16</v>
+      </c>
+      <c r="E424" s="4">
         <v>2</v>
       </c>
-      <c r="E424" s="6" t="inlineStr">
+      <c r="F424" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31457,9 +32732,12 @@
         </is>
       </c>
       <c r="D425" s="4">
+        <v>16</v>
+      </c>
+      <c r="E425" s="4">
         <v>3</v>
       </c>
-      <c r="E425" s="6" t="inlineStr">
+      <c r="F425" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31520,9 +32798,12 @@
         </is>
       </c>
       <c r="D426" s="4">
+        <v>16</v>
+      </c>
+      <c r="E426" s="4">
         <v>4</v>
       </c>
-      <c r="E426" s="6" t="inlineStr">
+      <c r="F426" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31583,9 +32864,12 @@
         </is>
       </c>
       <c r="D427" s="4">
+        <v>16</v>
+      </c>
+      <c r="E427" s="4">
         <v>5</v>
       </c>
-      <c r="E427" s="6" t="inlineStr">
+      <c r="F427" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31646,9 +32930,12 @@
         </is>
       </c>
       <c r="D428" s="4">
+        <v>16</v>
+      </c>
+      <c r="E428" s="4">
         <v>6</v>
       </c>
-      <c r="E428" s="6" t="inlineStr">
+      <c r="F428" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31709,9 +32996,12 @@
         </is>
       </c>
       <c r="D429" s="4">
+        <v>16</v>
+      </c>
+      <c r="E429" s="4">
         <v>7</v>
       </c>
-      <c r="E429" s="6" t="inlineStr">
+      <c r="F429" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31772,9 +33062,12 @@
         </is>
       </c>
       <c r="D430" s="4">
+        <v>16</v>
+      </c>
+      <c r="E430" s="4">
         <v>8</v>
       </c>
-      <c r="E430" s="6" t="inlineStr">
+      <c r="F430" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31835,9 +33128,12 @@
         </is>
       </c>
       <c r="D431" s="4">
+        <v>16</v>
+      </c>
+      <c r="E431" s="4">
         <v>9</v>
       </c>
-      <c r="E431" s="6" t="inlineStr">
+      <c r="F431" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31898,9 +33194,12 @@
         </is>
       </c>
       <c r="D432" s="4">
+        <v>16</v>
+      </c>
+      <c r="E432" s="4">
         <v>10</v>
       </c>
-      <c r="E432" s="6" t="inlineStr">
+      <c r="F432" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31961,9 +33260,12 @@
         </is>
       </c>
       <c r="D433" s="4">
+        <v>16</v>
+      </c>
+      <c r="E433" s="4">
         <v>11</v>
       </c>
-      <c r="E433" s="6" t="inlineStr">
+      <c r="F433" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32024,9 +33326,12 @@
         </is>
       </c>
       <c r="D434" s="4">
+        <v>16</v>
+      </c>
+      <c r="E434" s="4">
         <v>12</v>
       </c>
-      <c r="E434" s="6" t="inlineStr">
+      <c r="F434" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32087,9 +33392,12 @@
         </is>
       </c>
       <c r="D435" s="4">
+        <v>16</v>
+      </c>
+      <c r="E435" s="4">
         <v>13</v>
       </c>
-      <c r="E435" s="6" t="inlineStr">
+      <c r="F435" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32150,9 +33458,12 @@
         </is>
       </c>
       <c r="D436" s="4">
+        <v>16</v>
+      </c>
+      <c r="E436" s="4">
         <v>14</v>
       </c>
-      <c r="E436" s="6" t="inlineStr">
+      <c r="F436" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32213,9 +33524,12 @@
         </is>
       </c>
       <c r="D437" s="4">
+        <v>16</v>
+      </c>
+      <c r="E437" s="4">
         <v>15</v>
       </c>
-      <c r="E437" s="6" t="inlineStr">
+      <c r="F437" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32278,7 +33592,10 @@
       <c r="D438" s="4">
         <v>1</v>
       </c>
-      <c r="E438" s="6" t="inlineStr">
+      <c r="E438" s="4">
+        <v>1</v>
+      </c>
+      <c r="F438" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32339,9 +33656,12 @@
         </is>
       </c>
       <c r="D439" s="4">
+        <v>11</v>
+      </c>
+      <c r="E439" s="4">
         <v>1</v>
       </c>
-      <c r="E439" s="6" t="inlineStr">
+      <c r="F439" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32402,9 +33722,12 @@
         </is>
       </c>
       <c r="D440" s="4">
+        <v>11</v>
+      </c>
+      <c r="E440" s="4">
         <v>2</v>
       </c>
-      <c r="E440" s="6" t="inlineStr">
+      <c r="F440" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32465,9 +33788,12 @@
         </is>
       </c>
       <c r="D441" s="4">
+        <v>11</v>
+      </c>
+      <c r="E441" s="4">
         <v>3</v>
       </c>
-      <c r="E441" s="6" t="inlineStr">
+      <c r="F441" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32543,9 +33869,12 @@
         </is>
       </c>
       <c r="D442" s="4">
+        <v>11</v>
+      </c>
+      <c r="E442" s="4">
         <v>4</v>
       </c>
-      <c r="E442" s="6" t="inlineStr">
+      <c r="F442" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32651,9 +33980,12 @@
         </is>
       </c>
       <c r="D443" s="4">
+        <v>11</v>
+      </c>
+      <c r="E443" s="4">
         <v>5</v>
       </c>
-      <c r="E443" s="6" t="inlineStr">
+      <c r="F443" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32744,9 +34076,12 @@
         </is>
       </c>
       <c r="D444" s="4">
+        <v>11</v>
+      </c>
+      <c r="E444" s="4">
         <v>6</v>
       </c>
-      <c r="E444" s="6" t="inlineStr">
+      <c r="F444" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32815,9 +34150,12 @@
         </is>
       </c>
       <c r="D445" s="4">
+        <v>11</v>
+      </c>
+      <c r="E445" s="4">
         <v>7</v>
       </c>
-      <c r="E445" s="6" t="inlineStr">
+      <c r="F445" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32886,9 +34224,12 @@
         </is>
       </c>
       <c r="D446" s="4">
+        <v>11</v>
+      </c>
+      <c r="E446" s="4">
         <v>8</v>
       </c>
-      <c r="E446" s="6" t="inlineStr">
+      <c r="F446" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32957,9 +34298,12 @@
         </is>
       </c>
       <c r="D447" s="4">
+        <v>11</v>
+      </c>
+      <c r="E447" s="4">
         <v>9</v>
       </c>
-      <c r="E447" s="6" t="inlineStr">
+      <c r="F447" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33028,9 +34372,12 @@
         </is>
       </c>
       <c r="D448" s="4">
+        <v>11</v>
+      </c>
+      <c r="E448" s="4">
         <v>10</v>
       </c>
-      <c r="E448" s="6" t="inlineStr">
+      <c r="F448" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33108,7 +34455,10 @@
       <c r="D449" s="4">
         <v>11</v>
       </c>
-      <c r="E449" s="6" t="inlineStr">
+      <c r="E449" s="4">
+        <v>11</v>
+      </c>
+      <c r="F449" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33169,9 +34519,12 @@
         </is>
       </c>
       <c r="D450" s="4">
+        <v>7</v>
+      </c>
+      <c r="E450" s="4">
         <v>1</v>
       </c>
-      <c r="E450" s="6" t="inlineStr">
+      <c r="F450" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33241,9 +34594,12 @@
         </is>
       </c>
       <c r="D451" s="4">
+        <v>7</v>
+      </c>
+      <c r="E451" s="4">
         <v>2</v>
       </c>
-      <c r="E451" s="6" t="inlineStr">
+      <c r="F451" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33313,9 +34669,12 @@
         </is>
       </c>
       <c r="D452" s="4">
+        <v>7</v>
+      </c>
+      <c r="E452" s="4">
         <v>3</v>
       </c>
-      <c r="E452" s="6" t="inlineStr">
+      <c r="F452" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33385,9 +34744,12 @@
         </is>
       </c>
       <c r="D453" s="4">
+        <v>7</v>
+      </c>
+      <c r="E453" s="4">
         <v>4</v>
       </c>
-      <c r="E453" s="6" t="inlineStr">
+      <c r="F453" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33457,9 +34819,12 @@
         </is>
       </c>
       <c r="D454" s="4">
+        <v>7</v>
+      </c>
+      <c r="E454" s="4">
         <v>5</v>
       </c>
-      <c r="E454" s="6" t="inlineStr">
+      <c r="F454" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33529,9 +34894,12 @@
         </is>
       </c>
       <c r="D455" s="4">
+        <v>7</v>
+      </c>
+      <c r="E455" s="4">
         <v>6</v>
       </c>
-      <c r="E455" s="6" t="inlineStr">
+      <c r="F455" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33603,7 +34971,10 @@
       <c r="D456" s="4">
         <v>7</v>
       </c>
-      <c r="E456" s="6" t="inlineStr">
+      <c r="E456" s="4">
+        <v>7</v>
+      </c>
+      <c r="F456" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33673,9 +35044,12 @@
         </is>
       </c>
       <c r="D457" s="4">
+        <v>3</v>
+      </c>
+      <c r="E457" s="4">
         <v>1</v>
       </c>
-      <c r="E457" s="6" t="inlineStr">
+      <c r="F457" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33745,9 +35119,12 @@
         </is>
       </c>
       <c r="D458" s="4">
+        <v>3</v>
+      </c>
+      <c r="E458" s="4">
         <v>2</v>
       </c>
-      <c r="E458" s="6" t="inlineStr">
+      <c r="F458" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33819,7 +35196,10 @@
       <c r="D459" s="4">
         <v>3</v>
       </c>
-      <c r="E459" s="6" t="inlineStr">
+      <c r="E459" s="4">
+        <v>3</v>
+      </c>
+      <c r="F459" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33889,9 +35269,12 @@
         </is>
       </c>
       <c r="D460" s="4">
+        <v>4</v>
+      </c>
+      <c r="E460" s="4">
         <v>1</v>
       </c>
-      <c r="E460" s="6" t="inlineStr">
+      <c r="F460" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33961,9 +35344,12 @@
         </is>
       </c>
       <c r="D461" s="4">
+        <v>4</v>
+      </c>
+      <c r="E461" s="4">
         <v>2</v>
       </c>
-      <c r="E461" s="6" t="inlineStr">
+      <c r="F461" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34033,9 +35419,12 @@
         </is>
       </c>
       <c r="D462" s="4">
+        <v>4</v>
+      </c>
+      <c r="E462" s="4">
         <v>3</v>
       </c>
-      <c r="E462" s="6" t="inlineStr">
+      <c r="F462" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34107,7 +35496,10 @@
       <c r="D463" s="4">
         <v>4</v>
       </c>
-      <c r="E463" s="6" t="inlineStr">
+      <c r="E463" s="4">
+        <v>4</v>
+      </c>
+      <c r="F463" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34177,9 +35569,12 @@
         </is>
       </c>
       <c r="D464" s="4">
+        <v>2</v>
+      </c>
+      <c r="E464" s="4">
         <v>1</v>
       </c>
-      <c r="E464" s="6" t="inlineStr">
+      <c r="F464" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34251,7 +35646,10 @@
       <c r="D465" s="4">
         <v>2</v>
       </c>
-      <c r="E465" s="6" t="inlineStr">
+      <c r="E465" s="4">
+        <v>2</v>
+      </c>
+      <c r="F465" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34321,9 +35719,12 @@
         </is>
       </c>
       <c r="D466" s="4">
+        <v>6</v>
+      </c>
+      <c r="E466" s="4">
         <v>1</v>
       </c>
-      <c r="E466" s="6" t="inlineStr">
+      <c r="F466" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34393,9 +35794,12 @@
         </is>
       </c>
       <c r="D467" s="4">
+        <v>6</v>
+      </c>
+      <c r="E467" s="4">
         <v>2</v>
       </c>
-      <c r="E467" s="6" t="inlineStr">
+      <c r="F467" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34465,9 +35869,12 @@
         </is>
       </c>
       <c r="D468" s="4">
+        <v>6</v>
+      </c>
+      <c r="E468" s="4">
         <v>3</v>
       </c>
-      <c r="E468" s="6" t="inlineStr">
+      <c r="F468" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34537,9 +35944,12 @@
         </is>
       </c>
       <c r="D469" s="4">
+        <v>6</v>
+      </c>
+      <c r="E469" s="4">
         <v>4</v>
       </c>
-      <c r="E469" s="6" t="inlineStr">
+      <c r="F469" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34609,9 +36019,12 @@
         </is>
       </c>
       <c r="D470" s="4">
+        <v>6</v>
+      </c>
+      <c r="E470" s="4">
         <v>5</v>
       </c>
-      <c r="E470" s="6" t="inlineStr">
+      <c r="F470" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34683,7 +36096,10 @@
       <c r="D471" s="4">
         <v>6</v>
       </c>
-      <c r="E471" s="6" t="inlineStr">
+      <c r="E471" s="4">
+        <v>6</v>
+      </c>
+      <c r="F471" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34755,7 +36171,10 @@
       <c r="D472" s="4">
         <v>1</v>
       </c>
-      <c r="E472" s="6" t="inlineStr">
+      <c r="E472" s="4">
+        <v>1</v>
+      </c>
+      <c r="F472" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34827,7 +36246,10 @@
       <c r="D473" s="4">
         <v>1</v>
       </c>
-      <c r="E473" s="6" t="inlineStr">
+      <c r="E473" s="4">
+        <v>1</v>
+      </c>
+      <c r="F473" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34897,9 +36319,12 @@
         </is>
       </c>
       <c r="D474" s="4">
+        <v>2</v>
+      </c>
+      <c r="E474" s="4">
         <v>1</v>
       </c>
-      <c r="E474" s="6" t="inlineStr">
+      <c r="F474" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34971,7 +36396,10 @@
       <c r="D475" s="4">
         <v>2</v>
       </c>
-      <c r="E475" s="6" t="inlineStr">
+      <c r="E475" s="4">
+        <v>2</v>
+      </c>
+      <c r="F475" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35043,7 +36471,10 @@
       <c r="D476" s="4">
         <v>1</v>
       </c>
-      <c r="E476" s="6" t="inlineStr">
+      <c r="E476" s="4">
+        <v>1</v>
+      </c>
+      <c r="F476" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35113,9 +36544,12 @@
         </is>
       </c>
       <c r="D477" s="4">
+        <v>2</v>
+      </c>
+      <c r="E477" s="4">
         <v>1</v>
       </c>
-      <c r="E477" s="6" t="inlineStr">
+      <c r="F477" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35187,7 +36621,10 @@
       <c r="D478" s="4">
         <v>2</v>
       </c>
-      <c r="E478" s="6" t="inlineStr">
+      <c r="E478" s="4">
+        <v>2</v>
+      </c>
+      <c r="F478" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35259,7 +36696,10 @@
       <c r="D479" s="4">
         <v>1</v>
       </c>
-      <c r="E479" s="6" t="inlineStr">
+      <c r="E479" s="4">
+        <v>1</v>
+      </c>
+      <c r="F479" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35331,7 +36771,10 @@
       <c r="D480" s="4">
         <v>1</v>
       </c>
-      <c r="E480" s="6" t="inlineStr">
+      <c r="E480" s="4">
+        <v>1</v>
+      </c>
+      <c r="F480" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35401,9 +36844,12 @@
         </is>
       </c>
       <c r="D481" s="4">
+        <v>3</v>
+      </c>
+      <c r="E481" s="4">
         <v>1</v>
       </c>
-      <c r="E481" s="6" t="inlineStr">
+      <c r="F481" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35464,9 +36910,12 @@
         </is>
       </c>
       <c r="D482" s="4">
+        <v>3</v>
+      </c>
+      <c r="E482" s="4">
         <v>2</v>
       </c>
-      <c r="E482" s="6" t="inlineStr">
+      <c r="F482" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35538,7 +36987,10 @@
       <c r="D483" s="4">
         <v>3</v>
       </c>
-      <c r="E483" s="6" t="inlineStr">
+      <c r="E483" s="4">
+        <v>3</v>
+      </c>
+      <c r="F483" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35608,9 +37060,12 @@
         </is>
       </c>
       <c r="D484" s="4">
+        <v>18</v>
+      </c>
+      <c r="E484" s="4">
         <v>1</v>
       </c>
-      <c r="E484" s="6" t="inlineStr">
+      <c r="F484" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35680,9 +37135,12 @@
         </is>
       </c>
       <c r="D485" s="4">
+        <v>18</v>
+      </c>
+      <c r="E485" s="4">
         <v>2</v>
       </c>
-      <c r="E485" s="6" t="inlineStr">
+      <c r="F485" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35752,9 +37210,12 @@
         </is>
       </c>
       <c r="D486" s="4">
+        <v>18</v>
+      </c>
+      <c r="E486" s="4">
         <v>3</v>
       </c>
-      <c r="E486" s="6" t="inlineStr">
+      <c r="F486" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35824,9 +37285,12 @@
         </is>
       </c>
       <c r="D487" s="4">
+        <v>18</v>
+      </c>
+      <c r="E487" s="4">
         <v>4</v>
       </c>
-      <c r="E487" s="6" t="inlineStr">
+      <c r="F487" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35896,9 +37360,12 @@
         </is>
       </c>
       <c r="D488" s="4">
+        <v>18</v>
+      </c>
+      <c r="E488" s="4">
         <v>5</v>
       </c>
-      <c r="E488" s="6" t="inlineStr">
+      <c r="F488" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35968,9 +37435,12 @@
         </is>
       </c>
       <c r="D489" s="4">
+        <v>18</v>
+      </c>
+      <c r="E489" s="4">
         <v>6</v>
       </c>
-      <c r="E489" s="6" t="inlineStr">
+      <c r="F489" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36040,9 +37510,12 @@
         </is>
       </c>
       <c r="D490" s="4">
+        <v>18</v>
+      </c>
+      <c r="E490" s="4">
         <v>7</v>
       </c>
-      <c r="E490" s="6" t="inlineStr">
+      <c r="F490" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36112,9 +37585,12 @@
         </is>
       </c>
       <c r="D491" s="4">
+        <v>18</v>
+      </c>
+      <c r="E491" s="4">
         <v>8</v>
       </c>
-      <c r="E491" s="6" t="inlineStr">
+      <c r="F491" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36184,9 +37660,12 @@
         </is>
       </c>
       <c r="D492" s="4">
+        <v>18</v>
+      </c>
+      <c r="E492" s="4">
         <v>9</v>
       </c>
-      <c r="E492" s="6" t="inlineStr">
+      <c r="F492" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36256,9 +37735,12 @@
         </is>
       </c>
       <c r="D493" s="4">
+        <v>18</v>
+      </c>
+      <c r="E493" s="4">
         <v>10</v>
       </c>
-      <c r="E493" s="6" t="inlineStr">
+      <c r="F493" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36328,9 +37810,12 @@
         </is>
       </c>
       <c r="D494" s="4">
+        <v>18</v>
+      </c>
+      <c r="E494" s="4">
         <v>11</v>
       </c>
-      <c r="E494" s="6" t="inlineStr">
+      <c r="F494" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36400,9 +37885,12 @@
         </is>
       </c>
       <c r="D495" s="4">
+        <v>18</v>
+      </c>
+      <c r="E495" s="4">
         <v>12</v>
       </c>
-      <c r="E495" s="6" t="inlineStr">
+      <c r="F495" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36472,9 +37960,12 @@
         </is>
       </c>
       <c r="D496" s="4">
+        <v>18</v>
+      </c>
+      <c r="E496" s="4">
         <v>13</v>
       </c>
-      <c r="E496" s="6" t="inlineStr">
+      <c r="F496" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36544,9 +38035,12 @@
         </is>
       </c>
       <c r="D497" s="4">
+        <v>18</v>
+      </c>
+      <c r="E497" s="4">
         <v>14</v>
       </c>
-      <c r="E497" s="6" t="inlineStr">
+      <c r="F497" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36616,9 +38110,12 @@
         </is>
       </c>
       <c r="D498" s="4">
+        <v>18</v>
+      </c>
+      <c r="E498" s="4">
         <v>15</v>
       </c>
-      <c r="E498" s="6" t="inlineStr">
+      <c r="F498" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36688,9 +38185,12 @@
         </is>
       </c>
       <c r="D499" s="4">
+        <v>18</v>
+      </c>
+      <c r="E499" s="4">
         <v>16</v>
       </c>
-      <c r="E499" s="6" t="inlineStr">
+      <c r="F499" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36760,9 +38260,12 @@
         </is>
       </c>
       <c r="D500" s="4">
+        <v>18</v>
+      </c>
+      <c r="E500" s="4">
         <v>17</v>
       </c>
-      <c r="E500" s="6" t="inlineStr">
+      <c r="F500" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36834,7 +38337,10 @@
       <c r="D501" s="4">
         <v>18</v>
       </c>
-      <c r="E501" s="6" t="inlineStr">
+      <c r="E501" s="4">
+        <v>18</v>
+      </c>
+      <c r="F501" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36904,9 +38410,12 @@
         </is>
       </c>
       <c r="D502" s="4">
+        <v>17</v>
+      </c>
+      <c r="E502" s="4">
         <v>1</v>
       </c>
-      <c r="E502" s="6" t="inlineStr">
+      <c r="F502" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36976,9 +38485,12 @@
         </is>
       </c>
       <c r="D503" s="4">
+        <v>17</v>
+      </c>
+      <c r="E503" s="4">
         <v>2</v>
       </c>
-      <c r="E503" s="6" t="inlineStr">
+      <c r="F503" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37048,9 +38560,12 @@
         </is>
       </c>
       <c r="D504" s="4">
+        <v>17</v>
+      </c>
+      <c r="E504" s="4">
         <v>3</v>
       </c>
-      <c r="E504" s="6" t="inlineStr">
+      <c r="F504" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37120,9 +38635,12 @@
         </is>
       </c>
       <c r="D505" s="4">
+        <v>17</v>
+      </c>
+      <c r="E505" s="4">
         <v>4</v>
       </c>
-      <c r="E505" s="6" t="inlineStr">
+      <c r="F505" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37192,9 +38710,12 @@
         </is>
       </c>
       <c r="D506" s="4">
+        <v>17</v>
+      </c>
+      <c r="E506" s="4">
         <v>5</v>
       </c>
-      <c r="E506" s="6" t="inlineStr">
+      <c r="F506" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37264,9 +38785,12 @@
         </is>
       </c>
       <c r="D507" s="4">
+        <v>17</v>
+      </c>
+      <c r="E507" s="4">
         <v>6</v>
       </c>
-      <c r="E507" s="6" t="inlineStr">
+      <c r="F507" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37336,9 +38860,12 @@
         </is>
       </c>
       <c r="D508" s="4">
+        <v>17</v>
+      </c>
+      <c r="E508" s="4">
         <v>7</v>
       </c>
-      <c r="E508" s="6" t="inlineStr">
+      <c r="F508" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37408,9 +38935,12 @@
         </is>
       </c>
       <c r="D509" s="4">
+        <v>17</v>
+      </c>
+      <c r="E509" s="4">
         <v>8</v>
       </c>
-      <c r="E509" s="6" t="inlineStr">
+      <c r="F509" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37480,9 +39010,12 @@
         </is>
       </c>
       <c r="D510" s="4">
+        <v>17</v>
+      </c>
+      <c r="E510" s="4">
         <v>9</v>
       </c>
-      <c r="E510" s="6" t="inlineStr">
+      <c r="F510" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37552,9 +39085,12 @@
         </is>
       </c>
       <c r="D511" s="4">
+        <v>17</v>
+      </c>
+      <c r="E511" s="4">
         <v>10</v>
       </c>
-      <c r="E511" s="6" t="inlineStr">
+      <c r="F511" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37624,9 +39160,12 @@
         </is>
       </c>
       <c r="D512" s="4">
+        <v>17</v>
+      </c>
+      <c r="E512" s="4">
         <v>11</v>
       </c>
-      <c r="E512" s="6" t="inlineStr">
+      <c r="F512" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37696,9 +39235,12 @@
         </is>
       </c>
       <c r="D513" s="4">
+        <v>17</v>
+      </c>
+      <c r="E513" s="4">
         <v>12</v>
       </c>
-      <c r="E513" s="6" t="inlineStr">
+      <c r="F513" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37768,9 +39310,12 @@
         </is>
       </c>
       <c r="D514" s="4">
+        <v>17</v>
+      </c>
+      <c r="E514" s="4">
         <v>13</v>
       </c>
-      <c r="E514" s="6" t="inlineStr">
+      <c r="F514" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37840,9 +39385,12 @@
         </is>
       </c>
       <c r="D515" s="4">
+        <v>17</v>
+      </c>
+      <c r="E515" s="4">
         <v>14</v>
       </c>
-      <c r="E515" s="6" t="inlineStr">
+      <c r="F515" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37912,9 +39460,12 @@
         </is>
       </c>
       <c r="D516" s="4">
+        <v>17</v>
+      </c>
+      <c r="E516" s="4">
         <v>15</v>
       </c>
-      <c r="E516" s="6" t="inlineStr">
+      <c r="F516" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37984,9 +39535,12 @@
         </is>
       </c>
       <c r="D517" s="4">
+        <v>17</v>
+      </c>
+      <c r="E517" s="4">
         <v>16</v>
       </c>
-      <c r="E517" s="6" t="inlineStr">
+      <c r="F517" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38058,7 +39612,10 @@
       <c r="D518" s="4">
         <v>17</v>
       </c>
-      <c r="E518" s="6" t="inlineStr">
+      <c r="E518" s="4">
+        <v>17</v>
+      </c>
+      <c r="F518" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38128,9 +39685,12 @@
         </is>
       </c>
       <c r="D519" s="4">
+        <v>12</v>
+      </c>
+      <c r="E519" s="4">
         <v>1</v>
       </c>
-      <c r="E519" s="6" t="inlineStr">
+      <c r="F519" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38200,9 +39760,12 @@
         </is>
       </c>
       <c r="D520" s="4">
+        <v>12</v>
+      </c>
+      <c r="E520" s="4">
         <v>2</v>
       </c>
-      <c r="E520" s="6" t="inlineStr">
+      <c r="F520" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38272,9 +39835,12 @@
         </is>
       </c>
       <c r="D521" s="4">
+        <v>12</v>
+      </c>
+      <c r="E521" s="4">
         <v>3</v>
       </c>
-      <c r="E521" s="6" t="inlineStr">
+      <c r="F521" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38344,9 +39910,12 @@
         </is>
       </c>
       <c r="D522" s="4">
+        <v>12</v>
+      </c>
+      <c r="E522" s="4">
         <v>4</v>
       </c>
-      <c r="E522" s="6" t="inlineStr">
+      <c r="F522" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38416,9 +39985,12 @@
         </is>
       </c>
       <c r="D523" s="4">
+        <v>12</v>
+      </c>
+      <c r="E523" s="4">
         <v>5</v>
       </c>
-      <c r="E523" s="6" t="inlineStr">
+      <c r="F523" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38488,9 +40060,12 @@
         </is>
       </c>
       <c r="D524" s="4">
+        <v>12</v>
+      </c>
+      <c r="E524" s="4">
         <v>6</v>
       </c>
-      <c r="E524" s="6" t="inlineStr">
+      <c r="F524" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38560,9 +40135,12 @@
         </is>
       </c>
       <c r="D525" s="4">
+        <v>12</v>
+      </c>
+      <c r="E525" s="4">
         <v>7</v>
       </c>
-      <c r="E525" s="6" t="inlineStr">
+      <c r="F525" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38632,9 +40210,12 @@
         </is>
       </c>
       <c r="D526" s="4">
+        <v>12</v>
+      </c>
+      <c r="E526" s="4">
         <v>8</v>
       </c>
-      <c r="E526" s="6" t="inlineStr">
+      <c r="F526" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38704,9 +40285,12 @@
         </is>
       </c>
       <c r="D527" s="4">
+        <v>12</v>
+      </c>
+      <c r="E527" s="4">
         <v>9</v>
       </c>
-      <c r="E527" s="6" t="inlineStr">
+      <c r="F527" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38776,9 +40360,12 @@
         </is>
       </c>
       <c r="D528" s="4">
+        <v>12</v>
+      </c>
+      <c r="E528" s="4">
         <v>10</v>
       </c>
-      <c r="E528" s="6" t="inlineStr">
+      <c r="F528" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38848,9 +40435,12 @@
         </is>
       </c>
       <c r="D529" s="4">
+        <v>12</v>
+      </c>
+      <c r="E529" s="4">
         <v>11</v>
       </c>
-      <c r="E529" s="6" t="inlineStr">
+      <c r="F529" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38922,7 +40512,10 @@
       <c r="D530" s="4">
         <v>12</v>
       </c>
-      <c r="E530" s="6" t="inlineStr">
+      <c r="E530" s="4">
+        <v>12</v>
+      </c>
+      <c r="F530" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38992,9 +40585,12 @@
         </is>
       </c>
       <c r="D531" s="4">
+        <v>10</v>
+      </c>
+      <c r="E531" s="4">
         <v>1</v>
       </c>
-      <c r="E531" s="6" t="inlineStr">
+      <c r="F531" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39064,9 +40660,12 @@
         </is>
       </c>
       <c r="D532" s="4">
+        <v>10</v>
+      </c>
+      <c r="E532" s="4">
         <v>2</v>
       </c>
-      <c r="E532" s="6" t="inlineStr">
+      <c r="F532" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39136,9 +40735,12 @@
         </is>
       </c>
       <c r="D533" s="4">
+        <v>10</v>
+      </c>
+      <c r="E533" s="4">
         <v>3</v>
       </c>
-      <c r="E533" s="6" t="inlineStr">
+      <c r="F533" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39208,9 +40810,12 @@
         </is>
       </c>
       <c r="D534" s="4">
+        <v>10</v>
+      </c>
+      <c r="E534" s="4">
         <v>4</v>
       </c>
-      <c r="E534" s="6" t="inlineStr">
+      <c r="F534" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39280,9 +40885,12 @@
         </is>
       </c>
       <c r="D535" s="4">
+        <v>10</v>
+      </c>
+      <c r="E535" s="4">
         <v>5</v>
       </c>
-      <c r="E535" s="6" t="inlineStr">
+      <c r="F535" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39352,9 +40960,12 @@
         </is>
       </c>
       <c r="D536" s="4">
+        <v>10</v>
+      </c>
+      <c r="E536" s="4">
         <v>6</v>
       </c>
-      <c r="E536" s="6" t="inlineStr">
+      <c r="F536" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39424,9 +41035,12 @@
         </is>
       </c>
       <c r="D537" s="4">
+        <v>10</v>
+      </c>
+      <c r="E537" s="4">
         <v>7</v>
       </c>
-      <c r="E537" s="6" t="inlineStr">
+      <c r="F537" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39496,9 +41110,12 @@
         </is>
       </c>
       <c r="D538" s="4">
+        <v>10</v>
+      </c>
+      <c r="E538" s="4">
         <v>8</v>
       </c>
-      <c r="E538" s="6" t="inlineStr">
+      <c r="F538" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39568,9 +41185,12 @@
         </is>
       </c>
       <c r="D539" s="4">
+        <v>10</v>
+      </c>
+      <c r="E539" s="4">
         <v>9</v>
       </c>
-      <c r="E539" s="6" t="inlineStr">
+      <c r="F539" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39642,7 +41262,10 @@
       <c r="D540" s="4">
         <v>10</v>
       </c>
-      <c r="E540" s="6" t="inlineStr">
+      <c r="E540" s="4">
+        <v>10</v>
+      </c>
+      <c r="F540" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39712,9 +41335,12 @@
         </is>
       </c>
       <c r="D541" s="4">
+        <v>10</v>
+      </c>
+      <c r="E541" s="4">
         <v>1</v>
       </c>
-      <c r="E541" s="6" t="inlineStr">
+      <c r="F541" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39784,9 +41410,12 @@
         </is>
       </c>
       <c r="D542" s="4">
+        <v>10</v>
+      </c>
+      <c r="E542" s="4">
         <v>2</v>
       </c>
-      <c r="E542" s="6" t="inlineStr">
+      <c r="F542" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39856,9 +41485,12 @@
         </is>
       </c>
       <c r="D543" s="4">
+        <v>10</v>
+      </c>
+      <c r="E543" s="4">
         <v>3</v>
       </c>
-      <c r="E543" s="6" t="inlineStr">
+      <c r="F543" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39928,9 +41560,12 @@
         </is>
       </c>
       <c r="D544" s="4">
+        <v>10</v>
+      </c>
+      <c r="E544" s="4">
         <v>4</v>
       </c>
-      <c r="E544" s="6" t="inlineStr">
+      <c r="F544" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40000,9 +41635,12 @@
         </is>
       </c>
       <c r="D545" s="4">
+        <v>10</v>
+      </c>
+      <c r="E545" s="4">
         <v>5</v>
       </c>
-      <c r="E545" s="6" t="inlineStr">
+      <c r="F545" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40072,9 +41710,12 @@
         </is>
       </c>
       <c r="D546" s="4">
+        <v>10</v>
+      </c>
+      <c r="E546" s="4">
         <v>6</v>
       </c>
-      <c r="E546" s="6" t="inlineStr">
+      <c r="F546" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40144,9 +41785,12 @@
         </is>
       </c>
       <c r="D547" s="4">
+        <v>10</v>
+      </c>
+      <c r="E547" s="4">
         <v>7</v>
       </c>
-      <c r="E547" s="6" t="inlineStr">
+      <c r="F547" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40216,9 +41860,12 @@
         </is>
       </c>
       <c r="D548" s="4">
+        <v>10</v>
+      </c>
+      <c r="E548" s="4">
         <v>8</v>
       </c>
-      <c r="E548" s="6" t="inlineStr">
+      <c r="F548" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40288,9 +41935,12 @@
         </is>
       </c>
       <c r="D549" s="4">
+        <v>10</v>
+      </c>
+      <c r="E549" s="4">
         <v>9</v>
       </c>
-      <c r="E549" s="6" t="inlineStr">
+      <c r="F549" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40362,7 +42012,10 @@
       <c r="D550" s="4">
         <v>10</v>
       </c>
-      <c r="E550" s="6" t="inlineStr">
+      <c r="E550" s="4">
+        <v>10</v>
+      </c>
+      <c r="F550" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40432,9 +42085,12 @@
         </is>
       </c>
       <c r="D551" s="4">
+        <v>35</v>
+      </c>
+      <c r="E551" s="4">
         <v>1</v>
       </c>
-      <c r="E551" s="6" t="inlineStr">
+      <c r="F551" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40504,9 +42160,12 @@
         </is>
       </c>
       <c r="D552" s="4">
+        <v>35</v>
+      </c>
+      <c r="E552" s="4">
         <v>2</v>
       </c>
-      <c r="E552" s="6" t="inlineStr">
+      <c r="F552" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40576,9 +42235,12 @@
         </is>
       </c>
       <c r="D553" s="4">
+        <v>35</v>
+      </c>
+      <c r="E553" s="4">
         <v>3</v>
       </c>
-      <c r="E553" s="6" t="inlineStr">
+      <c r="F553" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40648,9 +42310,12 @@
         </is>
       </c>
       <c r="D554" s="4">
+        <v>35</v>
+      </c>
+      <c r="E554" s="4">
         <v>4</v>
       </c>
-      <c r="E554" s="6" t="inlineStr">
+      <c r="F554" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40720,9 +42385,12 @@
         </is>
       </c>
       <c r="D555" s="4">
+        <v>35</v>
+      </c>
+      <c r="E555" s="4">
         <v>5</v>
       </c>
-      <c r="E555" s="6" t="inlineStr">
+      <c r="F555" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40792,9 +42460,12 @@
         </is>
       </c>
       <c r="D556" s="4">
+        <v>35</v>
+      </c>
+      <c r="E556" s="4">
         <v>6</v>
       </c>
-      <c r="E556" s="6" t="inlineStr">
+      <c r="F556" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40864,9 +42535,12 @@
         </is>
       </c>
       <c r="D557" s="4">
+        <v>35</v>
+      </c>
+      <c r="E557" s="4">
         <v>7</v>
       </c>
-      <c r="E557" s="6" t="inlineStr">
+      <c r="F557" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40936,9 +42610,12 @@
         </is>
       </c>
       <c r="D558" s="4">
+        <v>35</v>
+      </c>
+      <c r="E558" s="4">
         <v>8</v>
       </c>
-      <c r="E558" s="6" t="inlineStr">
+      <c r="F558" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41008,9 +42685,12 @@
         </is>
       </c>
       <c r="D559" s="4">
+        <v>35</v>
+      </c>
+      <c r="E559" s="4">
         <v>9</v>
       </c>
-      <c r="E559" s="6" t="inlineStr">
+      <c r="F559" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41080,9 +42760,12 @@
         </is>
       </c>
       <c r="D560" s="4">
+        <v>35</v>
+      </c>
+      <c r="E560" s="4">
         <v>10</v>
       </c>
-      <c r="E560" s="6" t="inlineStr">
+      <c r="F560" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41152,9 +42835,12 @@
         </is>
       </c>
       <c r="D561" s="4">
+        <v>35</v>
+      </c>
+      <c r="E561" s="4">
         <v>11</v>
       </c>
-      <c r="E561" s="6" t="inlineStr">
+      <c r="F561" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41224,9 +42910,12 @@
         </is>
       </c>
       <c r="D562" s="4">
+        <v>35</v>
+      </c>
+      <c r="E562" s="4">
         <v>12</v>
       </c>
-      <c r="E562" s="6" t="inlineStr">
+      <c r="F562" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41296,9 +42985,12 @@
         </is>
       </c>
       <c r="D563" s="4">
+        <v>35</v>
+      </c>
+      <c r="E563" s="4">
         <v>13</v>
       </c>
-      <c r="E563" s="6" t="inlineStr">
+      <c r="F563" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41368,9 +43060,12 @@
         </is>
       </c>
       <c r="D564" s="4">
+        <v>35</v>
+      </c>
+      <c r="E564" s="4">
         <v>14</v>
       </c>
-      <c r="E564" s="6" t="inlineStr">
+      <c r="F564" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41440,9 +43135,12 @@
         </is>
       </c>
       <c r="D565" s="4">
+        <v>35</v>
+      </c>
+      <c r="E565" s="4">
         <v>15</v>
       </c>
-      <c r="E565" s="6" t="inlineStr">
+      <c r="F565" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41512,9 +43210,12 @@
         </is>
       </c>
       <c r="D566" s="4">
+        <v>35</v>
+      </c>
+      <c r="E566" s="4">
         <v>16</v>
       </c>
-      <c r="E566" s="6" t="inlineStr">
+      <c r="F566" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41584,9 +43285,12 @@
         </is>
       </c>
       <c r="D567" s="4">
+        <v>35</v>
+      </c>
+      <c r="E567" s="4">
         <v>17</v>
       </c>
-      <c r="E567" s="6" t="inlineStr">
+      <c r="F567" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41656,9 +43360,12 @@
         </is>
       </c>
       <c r="D568" s="4">
+        <v>35</v>
+      </c>
+      <c r="E568" s="4">
         <v>18</v>
       </c>
-      <c r="E568" s="6" t="inlineStr">
+      <c r="F568" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41728,9 +43435,12 @@
         </is>
       </c>
       <c r="D569" s="4">
+        <v>35</v>
+      </c>
+      <c r="E569" s="4">
         <v>19</v>
       </c>
-      <c r="E569" s="6" t="inlineStr">
+      <c r="F569" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41800,9 +43510,12 @@
         </is>
       </c>
       <c r="D570" s="4">
+        <v>35</v>
+      </c>
+      <c r="E570" s="4">
         <v>20</v>
       </c>
-      <c r="E570" s="6" t="inlineStr">
+      <c r="F570" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41856,253 +43569,335 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="246">
+  <mergeCells count="328">
     <mergeCell ref="A4:A7"/>
     <mergeCell ref="B4:B7"/>
     <mergeCell ref="C4:C7"/>
+    <mergeCell ref="D4:D7"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="B19:B21"/>
     <mergeCell ref="C19:C21"/>
+    <mergeCell ref="D19:D21"/>
     <mergeCell ref="A24:A27"/>
     <mergeCell ref="B24:B27"/>
     <mergeCell ref="C24:C27"/>
+    <mergeCell ref="D24:D27"/>
     <mergeCell ref="A31:A32"/>
     <mergeCell ref="B31:B32"/>
     <mergeCell ref="C31:C32"/>
+    <mergeCell ref="D31:D32"/>
     <mergeCell ref="A34:A35"/>
     <mergeCell ref="B34:B35"/>
     <mergeCell ref="C34:C35"/>
+    <mergeCell ref="D34:D35"/>
     <mergeCell ref="A36:A40"/>
     <mergeCell ref="B36:B40"/>
     <mergeCell ref="C36:C40"/>
+    <mergeCell ref="D36:D40"/>
     <mergeCell ref="A47:A50"/>
     <mergeCell ref="B47:B50"/>
     <mergeCell ref="C47:C50"/>
+    <mergeCell ref="D47:D50"/>
     <mergeCell ref="A52:A53"/>
     <mergeCell ref="B52:B53"/>
     <mergeCell ref="C52:C53"/>
+    <mergeCell ref="D52:D53"/>
     <mergeCell ref="A54:A55"/>
     <mergeCell ref="B54:B55"/>
     <mergeCell ref="C54:C55"/>
+    <mergeCell ref="D54:D55"/>
     <mergeCell ref="A56:A57"/>
     <mergeCell ref="B56:B57"/>
     <mergeCell ref="C56:C57"/>
+    <mergeCell ref="D56:D57"/>
     <mergeCell ref="A62:A63"/>
     <mergeCell ref="B62:B63"/>
     <mergeCell ref="C62:C63"/>
+    <mergeCell ref="D62:D63"/>
     <mergeCell ref="A64:A67"/>
     <mergeCell ref="B64:B67"/>
     <mergeCell ref="C64:C67"/>
+    <mergeCell ref="D64:D67"/>
     <mergeCell ref="A69:A70"/>
     <mergeCell ref="B69:B70"/>
     <mergeCell ref="C69:C70"/>
+    <mergeCell ref="D69:D70"/>
     <mergeCell ref="A71:A73"/>
     <mergeCell ref="B71:B73"/>
     <mergeCell ref="C71:C73"/>
+    <mergeCell ref="D71:D73"/>
     <mergeCell ref="A78:A80"/>
     <mergeCell ref="B78:B80"/>
     <mergeCell ref="C78:C80"/>
+    <mergeCell ref="D78:D80"/>
     <mergeCell ref="A83:A86"/>
     <mergeCell ref="B83:B86"/>
     <mergeCell ref="C83:C86"/>
+    <mergeCell ref="D83:D86"/>
     <mergeCell ref="A87:A88"/>
     <mergeCell ref="B87:B88"/>
     <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
     <mergeCell ref="A91:A92"/>
     <mergeCell ref="B91:B92"/>
     <mergeCell ref="C91:C92"/>
+    <mergeCell ref="D91:D92"/>
     <mergeCell ref="A95:A96"/>
     <mergeCell ref="B95:B96"/>
     <mergeCell ref="C95:C96"/>
+    <mergeCell ref="D95:D96"/>
     <mergeCell ref="A107:A109"/>
     <mergeCell ref="B107:B109"/>
     <mergeCell ref="C107:C109"/>
+    <mergeCell ref="D107:D109"/>
     <mergeCell ref="A117:A118"/>
     <mergeCell ref="B117:B118"/>
     <mergeCell ref="C117:C118"/>
+    <mergeCell ref="D117:D118"/>
     <mergeCell ref="A121:A122"/>
     <mergeCell ref="B121:B122"/>
     <mergeCell ref="C121:C122"/>
+    <mergeCell ref="D121:D122"/>
     <mergeCell ref="A138:A140"/>
     <mergeCell ref="B138:B140"/>
     <mergeCell ref="C138:C140"/>
+    <mergeCell ref="D138:D140"/>
     <mergeCell ref="A141:A142"/>
     <mergeCell ref="B141:B142"/>
     <mergeCell ref="C141:C142"/>
+    <mergeCell ref="D141:D142"/>
     <mergeCell ref="A159:A160"/>
     <mergeCell ref="B159:B160"/>
     <mergeCell ref="C159:C160"/>
+    <mergeCell ref="D159:D160"/>
     <mergeCell ref="A165:A166"/>
     <mergeCell ref="B165:B166"/>
     <mergeCell ref="C165:C166"/>
+    <mergeCell ref="D165:D166"/>
     <mergeCell ref="A168:A169"/>
     <mergeCell ref="B168:B169"/>
     <mergeCell ref="C168:C169"/>
+    <mergeCell ref="D168:D169"/>
     <mergeCell ref="A175:A176"/>
     <mergeCell ref="B175:B176"/>
     <mergeCell ref="C175:C176"/>
+    <mergeCell ref="D175:D176"/>
     <mergeCell ref="A181:A184"/>
     <mergeCell ref="B181:B184"/>
     <mergeCell ref="C181:C184"/>
+    <mergeCell ref="D181:D184"/>
     <mergeCell ref="A186:A189"/>
     <mergeCell ref="B186:B189"/>
     <mergeCell ref="C186:C189"/>
+    <mergeCell ref="D186:D189"/>
     <mergeCell ref="A190:A191"/>
     <mergeCell ref="B190:B191"/>
     <mergeCell ref="C190:C191"/>
+    <mergeCell ref="D190:D191"/>
     <mergeCell ref="A192:A193"/>
     <mergeCell ref="B192:B193"/>
     <mergeCell ref="C192:C193"/>
+    <mergeCell ref="D192:D193"/>
     <mergeCell ref="A194:A195"/>
     <mergeCell ref="B194:B195"/>
     <mergeCell ref="C194:C195"/>
+    <mergeCell ref="D194:D195"/>
     <mergeCell ref="A196:A207"/>
     <mergeCell ref="B196:B207"/>
     <mergeCell ref="C196:C207"/>
+    <mergeCell ref="D196:D207"/>
     <mergeCell ref="A208:A212"/>
     <mergeCell ref="B208:B212"/>
     <mergeCell ref="C208:C212"/>
+    <mergeCell ref="D208:D212"/>
     <mergeCell ref="A213:A216"/>
     <mergeCell ref="B213:B216"/>
     <mergeCell ref="C213:C216"/>
+    <mergeCell ref="D213:D216"/>
     <mergeCell ref="A217:A218"/>
     <mergeCell ref="B217:B218"/>
     <mergeCell ref="C217:C218"/>
+    <mergeCell ref="D217:D218"/>
     <mergeCell ref="A219:A224"/>
     <mergeCell ref="B219:B224"/>
     <mergeCell ref="C219:C224"/>
+    <mergeCell ref="D219:D224"/>
     <mergeCell ref="A228:A231"/>
     <mergeCell ref="B228:B231"/>
     <mergeCell ref="C228:C231"/>
+    <mergeCell ref="D228:D231"/>
     <mergeCell ref="A232:A242"/>
     <mergeCell ref="B232:B242"/>
     <mergeCell ref="C232:C242"/>
+    <mergeCell ref="D232:D242"/>
     <mergeCell ref="A243:A244"/>
     <mergeCell ref="B243:B244"/>
     <mergeCell ref="C243:C244"/>
+    <mergeCell ref="D243:D244"/>
     <mergeCell ref="A246:A249"/>
     <mergeCell ref="B246:B249"/>
     <mergeCell ref="C246:C249"/>
+    <mergeCell ref="D246:D249"/>
     <mergeCell ref="A250:A252"/>
     <mergeCell ref="B250:B252"/>
     <mergeCell ref="C250:C252"/>
+    <mergeCell ref="D250:D252"/>
     <mergeCell ref="A255:A274"/>
     <mergeCell ref="B255:B274"/>
     <mergeCell ref="C255:C274"/>
+    <mergeCell ref="D255:D274"/>
     <mergeCell ref="A276:A280"/>
     <mergeCell ref="B276:B280"/>
     <mergeCell ref="C276:C280"/>
+    <mergeCell ref="D276:D280"/>
     <mergeCell ref="A284:A285"/>
     <mergeCell ref="B284:B285"/>
     <mergeCell ref="C284:C285"/>
+    <mergeCell ref="D284:D285"/>
     <mergeCell ref="A287:A288"/>
     <mergeCell ref="B287:B288"/>
     <mergeCell ref="C287:C288"/>
+    <mergeCell ref="D287:D288"/>
     <mergeCell ref="A290:A291"/>
     <mergeCell ref="B290:B291"/>
     <mergeCell ref="C290:C291"/>
+    <mergeCell ref="D290:D291"/>
     <mergeCell ref="A294:A297"/>
     <mergeCell ref="B294:B297"/>
     <mergeCell ref="C294:C297"/>
+    <mergeCell ref="D294:D297"/>
     <mergeCell ref="A299:A310"/>
     <mergeCell ref="B299:B310"/>
     <mergeCell ref="C299:C310"/>
+    <mergeCell ref="D299:D310"/>
     <mergeCell ref="A311:A317"/>
     <mergeCell ref="B311:B317"/>
     <mergeCell ref="C311:C317"/>
+    <mergeCell ref="D311:D317"/>
     <mergeCell ref="A318:A324"/>
     <mergeCell ref="B318:B324"/>
     <mergeCell ref="C318:C324"/>
+    <mergeCell ref="D318:D324"/>
     <mergeCell ref="A325:A344"/>
     <mergeCell ref="B325:B344"/>
     <mergeCell ref="C325:C344"/>
+    <mergeCell ref="D325:D344"/>
     <mergeCell ref="A345:A350"/>
     <mergeCell ref="B345:B350"/>
     <mergeCell ref="C345:C350"/>
+    <mergeCell ref="D345:D350"/>
     <mergeCell ref="A352:A353"/>
     <mergeCell ref="B352:B353"/>
     <mergeCell ref="C352:C353"/>
+    <mergeCell ref="D352:D353"/>
     <mergeCell ref="A355:A374"/>
     <mergeCell ref="B355:B374"/>
     <mergeCell ref="C355:C374"/>
+    <mergeCell ref="D355:D374"/>
     <mergeCell ref="A378:A381"/>
     <mergeCell ref="B378:B381"/>
     <mergeCell ref="C378:C381"/>
+    <mergeCell ref="D378:D381"/>
     <mergeCell ref="A382:A383"/>
     <mergeCell ref="B382:B383"/>
     <mergeCell ref="C382:C383"/>
+    <mergeCell ref="D382:D383"/>
     <mergeCell ref="A385:A388"/>
     <mergeCell ref="B385:B388"/>
     <mergeCell ref="C385:C388"/>
+    <mergeCell ref="D385:D388"/>
     <mergeCell ref="A390:A405"/>
     <mergeCell ref="B390:B405"/>
     <mergeCell ref="C390:C405"/>
+    <mergeCell ref="D390:D405"/>
     <mergeCell ref="A406:A407"/>
     <mergeCell ref="B406:B407"/>
     <mergeCell ref="C406:C407"/>
+    <mergeCell ref="D406:D407"/>
     <mergeCell ref="A409:A410"/>
     <mergeCell ref="B409:B410"/>
     <mergeCell ref="C409:C410"/>
+    <mergeCell ref="D409:D410"/>
     <mergeCell ref="A411:A412"/>
     <mergeCell ref="B411:B412"/>
     <mergeCell ref="C411:C412"/>
+    <mergeCell ref="D411:D412"/>
     <mergeCell ref="A414:A416"/>
     <mergeCell ref="B414:B416"/>
     <mergeCell ref="C414:C416"/>
+    <mergeCell ref="D414:D416"/>
     <mergeCell ref="A418:A422"/>
     <mergeCell ref="B418:B422"/>
     <mergeCell ref="C418:C422"/>
+    <mergeCell ref="D418:D422"/>
     <mergeCell ref="A423:A437"/>
     <mergeCell ref="B423:B437"/>
     <mergeCell ref="C423:C437"/>
+    <mergeCell ref="D423:D437"/>
     <mergeCell ref="A439:A449"/>
     <mergeCell ref="B439:B449"/>
     <mergeCell ref="C439:C449"/>
+    <mergeCell ref="D439:D449"/>
     <mergeCell ref="A450:A456"/>
     <mergeCell ref="B450:B456"/>
     <mergeCell ref="C450:C456"/>
+    <mergeCell ref="D450:D456"/>
     <mergeCell ref="A457:A459"/>
     <mergeCell ref="B457:B459"/>
     <mergeCell ref="C457:C459"/>
+    <mergeCell ref="D457:D459"/>
     <mergeCell ref="A460:A463"/>
     <mergeCell ref="B460:B463"/>
     <mergeCell ref="C460:C463"/>
+    <mergeCell ref="D460:D463"/>
     <mergeCell ref="A464:A465"/>
     <mergeCell ref="B464:B465"/>
     <mergeCell ref="C464:C465"/>
+    <mergeCell ref="D464:D465"/>
     <mergeCell ref="A466:A471"/>
     <mergeCell ref="B466:B471"/>
     <mergeCell ref="C466:C471"/>
+    <mergeCell ref="D466:D471"/>
     <mergeCell ref="A474:A475"/>
     <mergeCell ref="B474:B475"/>
     <mergeCell ref="C474:C475"/>
+    <mergeCell ref="D474:D475"/>
     <mergeCell ref="A477:A478"/>
     <mergeCell ref="B477:B478"/>
     <mergeCell ref="C477:C478"/>
+    <mergeCell ref="D477:D478"/>
     <mergeCell ref="A481:A483"/>
     <mergeCell ref="B481:B483"/>
     <mergeCell ref="C481:C483"/>
+    <mergeCell ref="D481:D483"/>
     <mergeCell ref="A484:A501"/>
     <mergeCell ref="B484:B501"/>
     <mergeCell ref="C484:C501"/>
+    <mergeCell ref="D484:D501"/>
     <mergeCell ref="A502:A518"/>
     <mergeCell ref="B502:B518"/>
     <mergeCell ref="C502:C518"/>
+    <mergeCell ref="D502:D518"/>
     <mergeCell ref="A519:A530"/>
     <mergeCell ref="B519:B530"/>
     <mergeCell ref="C519:C530"/>
+    <mergeCell ref="D519:D530"/>
     <mergeCell ref="A531:A540"/>
     <mergeCell ref="B531:B540"/>
     <mergeCell ref="C531:C540"/>
+    <mergeCell ref="D531:D540"/>
     <mergeCell ref="A541:A550"/>
     <mergeCell ref="B541:B550"/>
     <mergeCell ref="C541:C550"/>
+    <mergeCell ref="D541:D550"/>
     <mergeCell ref="A551:A570"/>
     <mergeCell ref="B551:B570"/>
     <mergeCell ref="C551:C570"/>
+    <mergeCell ref="D551:D570"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
